--- a/scripts/property_count.xlsx
+++ b/scripts/property_count.xlsx
@@ -21055,7 +21055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D855"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -21454,13 +21454,13 @@
         <v>Ali</v>
       </c>
       <c r="B29" t="str">
-        <v>aabbac04@gmail.com</v>
+        <v>info@swiftpropertygroup.co.uk</v>
       </c>
       <c r="C29" t="str">
-        <v>07788 893009</v>
+        <v>07480944770</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>Swift Property Group</v>
       </c>
     </row>
     <row r="30">
@@ -21468,13 +21468,13 @@
         <v>Ali</v>
       </c>
       <c r="B30" t="str">
-        <v>info@swiftpropertygroup.co.uk</v>
+        <v>aabbac04@gmail.com</v>
       </c>
       <c r="C30" t="str">
-        <v>07480944770</v>
+        <v>07788 893009</v>
       </c>
       <c r="D30" t="str">
-        <v>Swift Property Group</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -21916,13 +21916,13 @@
         <v>Andy Glynne</v>
       </c>
       <c r="B62" t="str">
-        <v>hello@stonesthrowapartments.uk</v>
+        <v>ag@jag-pl.com</v>
       </c>
       <c r="C62" t="str">
-        <v>07968696275</v>
+        <v xml:space="preserve">07845 672987 </v>
       </c>
       <c r="D62" t="str">
-        <v>Stones Throw Apartments</v>
+        <v>Stone Throw Apartments</v>
       </c>
     </row>
     <row r="63">
@@ -21930,13 +21930,13 @@
         <v>Andy Glynne</v>
       </c>
       <c r="B63" t="str">
-        <v>ag@jag-pl.com</v>
+        <v>hello@stonesthrowapartments.uk</v>
       </c>
       <c r="C63" t="str">
-        <v xml:space="preserve">07845 672987 </v>
+        <v>07968696275</v>
       </c>
       <c r="D63" t="str">
-        <v>Stone Throw Apartments</v>
+        <v>Stones Throw Apartments</v>
       </c>
     </row>
     <row r="64">
@@ -23442,10 +23442,10 @@
         <v>Daniel Vince</v>
       </c>
       <c r="B171" t="str">
-        <v>sehdisdh@hsadadk.co.uk</v>
+        <v>daniel@fakeva.com</v>
       </c>
       <c r="C171" t="str">
-        <v>07909323232</v>
+        <v>07909 323232</v>
       </c>
       <c r="D171" t="str">
         <v/>
@@ -23456,10 +23456,10 @@
         <v>Daniel Vince</v>
       </c>
       <c r="B172" t="str">
-        <v>daniel@fakeva.com</v>
+        <v>sehdisdh@hsadadk.co.uk</v>
       </c>
       <c r="C172" t="str">
-        <v>07909 323232</v>
+        <v>07909323232</v>
       </c>
       <c r="D172" t="str">
         <v/>
@@ -23582,13 +23582,13 @@
         <v>David</v>
       </c>
       <c r="B181" t="str">
-        <v>info@luxstayventures.com</v>
+        <v>wer@ert.com</v>
       </c>
       <c r="C181" t="str">
-        <v>07840052351</v>
+        <v>07392852104</v>
       </c>
       <c r="D181" t="str">
-        <v>Luxe stay ventures</v>
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -23596,13 +23596,13 @@
         <v>David</v>
       </c>
       <c r="B182" t="str">
-        <v>wer@ert.com</v>
+        <v>info@luxstayventures.com</v>
       </c>
       <c r="C182" t="str">
-        <v>07392852104</v>
+        <v>07840052351</v>
       </c>
       <c r="D182" t="str">
-        <v/>
+        <v>Luxe stay ventures</v>
       </c>
     </row>
     <row r="183">
@@ -26033,13 +26033,13 @@
         <v>Jesse John</v>
       </c>
       <c r="B356" t="str">
-        <v>hello@comfyworkers.com</v>
+        <v>admin@changeproperty.co.uk</v>
       </c>
       <c r="C356" t="str">
-        <v>0330 223 1412</v>
+        <v>07809682635</v>
       </c>
       <c r="D356" t="str">
-        <v>Comfy Workers</v>
+        <v>Change Property</v>
       </c>
     </row>
     <row r="357">
@@ -26047,13 +26047,13 @@
         <v>Jesse John</v>
       </c>
       <c r="B357" t="str">
-        <v>admin@changeproperty.co.uk</v>
+        <v>hello@comfyworkers.com</v>
       </c>
       <c r="C357" t="str">
-        <v>07809682635</v>
+        <v>0330 223 1412</v>
       </c>
       <c r="D357" t="str">
-        <v>Change Property</v>
+        <v>Comfy Workers</v>
       </c>
     </row>
     <row r="358">
@@ -26061,13 +26061,13 @@
         <v>Jessica</v>
       </c>
       <c r="B358" t="str">
-        <v>bookings@myhomeisyours.co</v>
+        <v>accomodation@primalestates.co.uk</v>
       </c>
       <c r="C358" t="str">
-        <v>+44 330 043 4566</v>
+        <v>07470049689</v>
       </c>
       <c r="D358" t="str">
-        <v/>
+        <v>Primal Estates</v>
       </c>
     </row>
     <row r="359">
@@ -26075,13 +26075,13 @@
         <v>Jessica</v>
       </c>
       <c r="B359" t="str">
-        <v>accomodation@primalestates.co.uk</v>
+        <v>bookings@myhomeisyours.co</v>
       </c>
       <c r="C359" t="str">
-        <v>07470049689</v>
+        <v>+44 330 043 4566</v>
       </c>
       <c r="D359" t="str">
-        <v>Primal Estates</v>
+        <v/>
       </c>
     </row>
     <row r="360">
@@ -27559,13 +27559,13 @@
         <v>Louis</v>
       </c>
       <c r="B465" t="str">
-        <v>enquiries@basingstokeapartmentservice.co.uk</v>
+        <v>Info@harrisandcoestates.co.uk</v>
       </c>
       <c r="C465" t="str">
-        <v>01256479062</v>
+        <v>01253876515</v>
       </c>
       <c r="D465" t="str">
-        <v/>
+        <v>Harris &amp; Co.</v>
       </c>
     </row>
     <row r="466">
@@ -27573,13 +27573,13 @@
         <v>Louis</v>
       </c>
       <c r="B466" t="str">
-        <v>Info@harrisandcoestates.co.uk</v>
+        <v>enquiries@basingstokeapartmentservice.co.uk</v>
       </c>
       <c r="C466" t="str">
-        <v>01253876515</v>
+        <v>01256479062</v>
       </c>
       <c r="D466" t="str">
-        <v>Harris &amp; Co.</v>
+        <v/>
       </c>
     </row>
     <row r="467">
@@ -28060,139 +28060,139 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v xml:space="preserve">Matt </v>
+        <v>Matt</v>
       </c>
       <c r="B501" t="str">
-        <v>info@onestopshortlets.co.uk</v>
+        <v>info@railwayapartments.co.uk</v>
       </c>
       <c r="C501" t="str">
-        <v>07736 752312</v>
+        <v>07498220201</v>
       </c>
       <c r="D501" t="str">
-        <v>One Stop Short Lets</v>
+        <v>Railway Hotel Apartments</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v xml:space="preserve">Matt &amp; Steph </v>
+        <v xml:space="preserve">Matt </v>
       </c>
       <c r="B502" t="str">
-        <v>hello@citysuperhost.com</v>
+        <v>info@onestopshortlets.co.uk</v>
       </c>
       <c r="C502" t="str">
-        <v>07394 137754</v>
+        <v>07736 752312</v>
       </c>
       <c r="D502" t="str">
-        <v>Citysuperhost</v>
+        <v>One Stop Short Lets</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Matt (&amp; Lynley)</v>
+        <v xml:space="preserve">Matt &amp; Steph </v>
       </c>
       <c r="B503" t="str">
-        <v>matt@fakeemail.com</v>
+        <v>hello@citysuperhost.com</v>
       </c>
       <c r="C503" t="str">
-        <v>07982249685</v>
+        <v>07394 137754</v>
       </c>
       <c r="D503" t="str">
-        <v>Airbnb</v>
+        <v>Citysuperhost</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Matt Watson</v>
+        <v>Matt (&amp; Lynley)</v>
       </c>
       <c r="B504" t="str">
-        <v>MJWPropertyGroup@outlook.com</v>
+        <v>matt@fakeemail.com</v>
       </c>
       <c r="C504" t="str">
-        <v>07742040885</v>
+        <v>07982249685</v>
       </c>
       <c r="D504" t="str">
-        <v>MJWPropertyGroup</v>
+        <v>Airbnb</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Matthew</v>
+        <v>Matt Watson</v>
       </c>
       <c r="B505" t="str">
-        <v>support@mypropertyhost.com</v>
+        <v>MJWPropertyGroup@outlook.com</v>
       </c>
       <c r="C505" t="str">
-        <v>020 3773 5264</v>
+        <v>07742040885</v>
       </c>
       <c r="D505" t="str">
-        <v xml:space="preserve">My Property Host </v>
+        <v>MJWPropertyGroup</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Matthew Porsz</v>
+        <v>Matthew</v>
       </c>
       <c r="B506" t="str">
-        <v>mattairlondon@gmail.com</v>
+        <v>support@mypropertyhost.com</v>
       </c>
       <c r="C506" t="str">
-        <v>+44 7940 707508</v>
+        <v>020 3773 5264</v>
       </c>
       <c r="D506" t="str">
-        <v>Airbnb Community Host</v>
+        <v xml:space="preserve">My Property Host </v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v xml:space="preserve">Maurice </v>
+        <v>Matthew Porsz</v>
       </c>
       <c r="B507" t="str">
-        <v>maurice@AirbnbNOT.com</v>
+        <v>mattairlondon@gmail.com</v>
       </c>
       <c r="C507" t="str">
-        <v>+447516 056 149</v>
+        <v>+44 7940 707508</v>
       </c>
       <c r="D507" t="str">
-        <v/>
+        <v>Airbnb Community Host</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Maxim Marcenco</v>
+        <v xml:space="preserve">Maurice </v>
       </c>
       <c r="B508" t="str">
-        <v>info@delightproperties.co.uk</v>
+        <v>maurice@AirbnbNOT.com</v>
       </c>
       <c r="C508" t="str">
-        <v>07736729370</v>
+        <v>+447516 056 149</v>
       </c>
       <c r="D508" t="str">
-        <v>Delight Residential Properties</v>
+        <v/>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Maya Devi</v>
+        <v>Maxim Marcenco</v>
       </c>
       <c r="B509" t="str">
-        <v>Fake@gmail.com</v>
+        <v>info@delightproperties.co.uk</v>
       </c>
       <c r="C509" t="str">
-        <v>07488562002</v>
+        <v>07736729370</v>
       </c>
       <c r="D509" t="str">
-        <v/>
+        <v>Delight Residential Properties</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Megan</v>
+        <v>Maya Devi</v>
       </c>
       <c r="B510" t="str">
-        <v>megan@luxekeystays.com</v>
+        <v>Fake@gmail.com</v>
       </c>
       <c r="C510" t="str">
-        <v>07538441257</v>
+        <v>07488562002</v>
       </c>
       <c r="D510" t="str">
         <v/>
@@ -28200,10 +28200,10 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Megan - MR Retreats</v>
+        <v>Megan</v>
       </c>
       <c r="B511" t="str">
-        <v>meganmurraylane@gmail.com</v>
+        <v>megan@luxekeystays.com</v>
       </c>
       <c r="C511" t="str">
         <v>07538441257</v>
@@ -28214,139 +28214,139 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Mehdi</v>
+        <v>Megan - MR Retreats</v>
       </c>
       <c r="B512" t="str">
-        <v>zuhal_propertyinvestments@hotmail.com</v>
+        <v>meganmurraylane@gmail.com</v>
       </c>
       <c r="C512" t="str">
-        <v>075510 38886</v>
+        <v>07538441257</v>
       </c>
       <c r="D512" t="str">
-        <v>Zuhal Property Investments</v>
+        <v/>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mercan</v>
+        <v>Mehdi</v>
       </c>
       <c r="B513" t="str">
-        <v>noemail@fake.com</v>
+        <v>zuhal_propertyinvestments@hotmail.com</v>
       </c>
       <c r="C513" t="str">
-        <v>07903472884</v>
+        <v>075510 38886</v>
       </c>
       <c r="D513" t="str">
-        <v/>
+        <v>Zuhal Property Investments</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v xml:space="preserve">Mia Baker </v>
+        <v>Mercan</v>
       </c>
       <c r="B514" t="str">
-        <v>mia@reddoorpropertygroup.co.uk</v>
+        <v>noemail@fake.com</v>
       </c>
       <c r="C514" t="str">
-        <v>07763491451</v>
+        <v>07903472884</v>
       </c>
       <c r="D514" t="str">
-        <v>Red Door Stays</v>
+        <v/>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Mia | Ismi Properties</v>
+        <v xml:space="preserve">Mia Baker </v>
       </c>
       <c r="B515" t="str">
-        <v>ismiproperties@gmail.com</v>
+        <v>mia@reddoorpropertygroup.co.uk</v>
       </c>
       <c r="C515" t="str">
-        <v>07557769298</v>
+        <v>07763491451</v>
       </c>
       <c r="D515" t="str">
-        <v/>
+        <v>Red Door Stays</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Michael Christodoulou</v>
+        <v>Mia | Ismi Properties</v>
       </c>
       <c r="B516" t="str">
-        <v>info@headsonbeds.co.uk</v>
+        <v>ismiproperties@gmail.com</v>
       </c>
       <c r="C516" t="str">
-        <v>07939524973</v>
+        <v>07557769298</v>
       </c>
       <c r="D516" t="str">
-        <v>London and County Property Group Ltd</v>
+        <v/>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Michael Greaves</v>
+        <v>Michael Christodoulou</v>
       </c>
       <c r="B517" t="str">
-        <v>poppins@fakeemail.com</v>
+        <v>info@headsonbeds.co.uk</v>
       </c>
       <c r="C517" t="str">
-        <v>07977454551</v>
+        <v>07939524973</v>
       </c>
       <c r="D517" t="str">
-        <v>Poppins Short Stays</v>
+        <v>London and County Property Group Ltd</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Michelle</v>
+        <v>Michael Greaves</v>
       </c>
       <c r="B518" t="str">
-        <v>michelle@gmail.com</v>
+        <v>poppins@fakeemail.com</v>
       </c>
       <c r="C518" t="str">
-        <v>07492 058851</v>
+        <v>07977454551</v>
       </c>
       <c r="D518" t="str">
-        <v/>
+        <v>Poppins Short Stays</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Michelle Dyer</v>
+        <v>Michelle</v>
       </c>
       <c r="B519" t="str">
-        <v>reservations@citysuites.com</v>
+        <v>michelle@gmail.com</v>
       </c>
       <c r="C519" t="str">
-        <v>07377059776</v>
+        <v>07492 058851</v>
       </c>
       <c r="D519" t="str">
-        <v>Citysuites</v>
+        <v/>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Milena</v>
+        <v>Michelle Dyer</v>
       </c>
       <c r="B520" t="str">
-        <v>milena@Airbnb.com</v>
+        <v>reservations@citysuites.com</v>
       </c>
       <c r="C520" t="str">
-        <v>+447747624744</v>
+        <v>07377059776</v>
       </c>
       <c r="D520" t="str">
-        <v/>
+        <v>Citysuites</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Miranda Peel</v>
+        <v>Milena</v>
       </c>
       <c r="B521" t="str">
-        <v>bookings@no12apartments.co.uk</v>
+        <v>milena@Airbnb.com</v>
       </c>
       <c r="C521" t="str">
-        <v xml:space="preserve"> 07397 902582</v>
+        <v>+447747624744</v>
       </c>
       <c r="D521" t="str">
         <v/>
@@ -28354,13 +28354,13 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Miriam Allen</v>
+        <v>Miranda Peel</v>
       </c>
       <c r="B522" t="str">
-        <v>host@shortstayuk.co.uk</v>
+        <v>bookings@no12apartments.co.uk</v>
       </c>
       <c r="C522" t="str">
-        <v>+447534455926</v>
+        <v xml:space="preserve"> 07397 902582</v>
       </c>
       <c r="D522" t="str">
         <v/>
@@ -28368,13 +28368,13 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Mo</v>
+        <v>Miriam Allen</v>
       </c>
       <c r="B523" t="str">
-        <v>info@milamanagement.co.uk</v>
+        <v>host@shortstayuk.co.uk</v>
       </c>
       <c r="C523" t="str">
-        <v>+447888003322</v>
+        <v>+447534455926</v>
       </c>
       <c r="D523" t="str">
         <v/>
@@ -28382,58 +28382,58 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Mo PE</v>
+        <v>Mo</v>
       </c>
       <c r="B524" t="str">
-        <v>MO@GMAIL.COM</v>
+        <v>info@milamanagement.co.uk</v>
       </c>
       <c r="C524" t="str">
-        <v>+44 7956 269737</v>
+        <v>+447888003322</v>
       </c>
       <c r="D524" t="str">
-        <v>A &amp; Z Enterprise Ltd</v>
+        <v/>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Modou | Hayy Apart hotels</v>
+        <v>Mo PE</v>
       </c>
       <c r="B525" t="str">
-        <v>enquiry@hayy.co.uk</v>
+        <v>MO@GMAIL.COM</v>
       </c>
       <c r="C525" t="str">
-        <v>07759 264328</v>
+        <v>+44 7956 269737</v>
       </c>
       <c r="D525" t="str">
-        <v/>
+        <v>A &amp; Z Enterprise Ltd</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Moeed Chaudhry</v>
+        <v>Modou | Hayy Apart hotels</v>
       </c>
       <c r="B526" t="str">
-        <v>famida.ltd@uwclub.net</v>
+        <v>enquiry@hayy.co.uk</v>
       </c>
       <c r="C526" t="str">
-        <v>07542 543199</v>
+        <v>07759 264328</v>
       </c>
       <c r="D526" t="str">
-        <v>Famida Properties Ltd</v>
+        <v/>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Mohammed</v>
+        <v>Moeed Chaudhry</v>
       </c>
       <c r="B527" t="str">
-        <v>citistays@aol.com</v>
+        <v>famida.ltd@uwclub.net</v>
       </c>
       <c r="C527" t="str">
-        <v>07985589822</v>
+        <v>07542 543199</v>
       </c>
       <c r="D527" t="str">
-        <v>City Stays</v>
+        <v>Famida Properties Ltd</v>
       </c>
     </row>
     <row r="528">
@@ -28441,122 +28441,122 @@
         <v>Mohammed</v>
       </c>
       <c r="B528" t="str">
-        <v>newport@quayapartments.co.uk</v>
+        <v>citistays@aol.com</v>
       </c>
       <c r="C528" t="str">
-        <v>01633386619</v>
+        <v>07985589822</v>
       </c>
       <c r="D528" t="str">
-        <v/>
+        <v>City Stays</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v xml:space="preserve">Mohammed Rameez Nabibux </v>
+        <v>Mohammed</v>
       </c>
       <c r="B529" t="str">
-        <v>maninvestors2025@gmail.com</v>
+        <v>newport@quayapartments.co.uk</v>
       </c>
       <c r="C529" t="str">
-        <v>+44 7714003444</v>
+        <v>01633386619</v>
       </c>
       <c r="D529" t="str">
-        <v>Man Investors</v>
+        <v/>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Mohammed | CITI Apartment Ltd</v>
+        <v xml:space="preserve">Mohammed Rameez Nabibux </v>
       </c>
       <c r="B530" t="str">
-        <v>mo@fpjwf.com</v>
+        <v>maninvestors2025@gmail.com</v>
       </c>
       <c r="C530" t="str">
-        <v>07985589822</v>
+        <v>+44 7714003444</v>
       </c>
       <c r="D530" t="str">
-        <v/>
+        <v>Man Investors</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Monarch House Serviced Apartments</v>
+        <v>Mohammed | CITI Apartment Ltd</v>
       </c>
       <c r="B531" t="str">
-        <v>sales@monarchhouse.co.uk</v>
+        <v>mo@fpjwf.com</v>
       </c>
       <c r="C531" t="str">
-        <v>+44 (0)20 7890 8800</v>
+        <v>07985589822</v>
       </c>
       <c r="D531" t="str">
-        <v>Monarch House</v>
+        <v/>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Monika &amp; Davij</v>
+        <v>Monarch House Serviced Apartments</v>
       </c>
       <c r="B532" t="str">
-        <v>info@dmshelter.co.uk</v>
+        <v>sales@monarchhouse.co.uk</v>
       </c>
       <c r="C532" t="str">
-        <v>+447759178232</v>
+        <v>+44 (0)20 7890 8800</v>
       </c>
       <c r="D532" t="str">
-        <v/>
+        <v>Monarch House</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Mugo Rutsito</v>
+        <v>Monika &amp; Davij</v>
       </c>
       <c r="B533" t="str">
-        <v>Info@mbiz-i.co.uk</v>
+        <v>info@dmshelter.co.uk</v>
       </c>
       <c r="C533" t="str">
-        <v>+447985256690</v>
+        <v>+447759178232</v>
       </c>
       <c r="D533" t="str">
-        <v>MBiZ Short Stays</v>
+        <v/>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Musthaq</v>
+        <v>Mugo Rutsito</v>
       </c>
       <c r="B534" t="str">
-        <v>fdsgfjfg@fvjhesdfjh.com</v>
+        <v>Info@mbiz-i.co.uk</v>
       </c>
       <c r="C534" t="str">
-        <v>07707714932</v>
+        <v>+447985256690</v>
       </c>
       <c r="D534" t="str">
-        <v xml:space="preserve">MI serviced accommodation </v>
+        <v>MBiZ Short Stays</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Myles</v>
+        <v>Musthaq</v>
       </c>
       <c r="B535" t="str">
-        <v>bookings@murraystays.co.uk</v>
+        <v>fdsgfjfg@fvjhesdfjh.com</v>
       </c>
       <c r="C535" t="str">
-        <v>07828117537</v>
+        <v>07707714932</v>
       </c>
       <c r="D535" t="str">
-        <v/>
+        <v xml:space="preserve">MI serviced accommodation </v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>N&amp;N Stays</v>
+        <v>Myles</v>
       </c>
       <c r="B536" t="str">
-        <v>info@nandnstays.co.uk</v>
+        <v>bookings@murraystays.co.uk</v>
       </c>
       <c r="C536" t="str">
-        <v>01225 595686</v>
+        <v>07828117537</v>
       </c>
       <c r="D536" t="str">
         <v/>
@@ -28564,44 +28564,44 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Na'im / Bruce</v>
+        <v>N&amp;N Stays</v>
       </c>
       <c r="B537" t="str">
-        <v>bruce@paymanclub.com</v>
+        <v>info@nandnstays.co.uk</v>
       </c>
       <c r="C537" t="str">
-        <v>0333 4444 324</v>
+        <v>01225 595686</v>
       </c>
       <c r="D537" t="str">
-        <v>Hertford Serviced Apartments</v>
+        <v/>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Nabil Sharif - VERY poor experience</v>
+        <v>Na'im / Bruce</v>
       </c>
       <c r="B538" t="str">
-        <v>info@finesseacquisitions.co.uk</v>
+        <v>bruce@paymanclub.com</v>
       </c>
       <c r="C538" t="str">
-        <v>07939201686</v>
+        <v>0333 4444 324</v>
       </c>
       <c r="D538" t="str">
-        <v>Finesse Acquisitions Ltd</v>
+        <v>Hertford Serviced Apartments</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Nadia</v>
+        <v>Nabil Sharif - VERY poor experience</v>
       </c>
       <c r="B539" t="str">
-        <v>nadia.kamal@yahoo.co.uk</v>
+        <v>info@finesseacquisitions.co.uk</v>
       </c>
       <c r="C539" t="str">
-        <v>07949 566132</v>
+        <v>07939201686</v>
       </c>
       <c r="D539" t="str">
-        <v/>
+        <v>Finesse Acquisitions Ltd</v>
       </c>
     </row>
     <row r="540">
@@ -28609,94 +28609,94 @@
         <v>Nadia</v>
       </c>
       <c r="B540" t="str">
-        <v>hello@ovitzia.com</v>
+        <v>nadia.kamal@yahoo.co.uk</v>
       </c>
       <c r="C540" t="str">
-        <v>07387 296542</v>
+        <v>07949 566132</v>
       </c>
       <c r="D540" t="str">
-        <v>Ovitzia</v>
+        <v/>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Nagarju Bapanapalli</v>
+        <v>Nadia</v>
       </c>
       <c r="B541" t="str">
-        <v>notreal@gmail.com</v>
+        <v>hello@ovitzia.com</v>
       </c>
       <c r="C541" t="str">
-        <v>07356264009</v>
+        <v>07387 296542</v>
       </c>
       <c r="D541" t="str">
-        <v/>
+        <v>Ovitzia</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Nana Enyo</v>
+        <v>Nagarju Bapanapalli</v>
       </c>
       <c r="B542" t="str">
-        <v>yitseienyolimited@gmail.com</v>
+        <v>notreal@gmail.com</v>
       </c>
       <c r="C542" t="str">
-        <v>07505444251</v>
+        <v>07356264009</v>
       </c>
       <c r="D542" t="str">
-        <v>Enyo House</v>
+        <v/>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Nancy</v>
+        <v>Nana Enyo</v>
       </c>
       <c r="B543" t="str">
-        <v>nancy@gmail.com</v>
+        <v>yitseienyolimited@gmail.com</v>
       </c>
       <c r="C543" t="str">
-        <v>07912441658</v>
+        <v>07505444251</v>
       </c>
       <c r="D543" t="str">
-        <v>direct2host</v>
+        <v>Enyo House</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Natalia Banas</v>
+        <v>Nancy</v>
       </c>
       <c r="B544" t="str">
-        <v>info@nbaccommodation.co.uk</v>
+        <v>nancy@gmail.com</v>
       </c>
       <c r="C544" t="str">
-        <v>07729919597</v>
+        <v>07912441658</v>
       </c>
       <c r="D544" t="str">
-        <v>NB Short Stay</v>
+        <v>direct2host</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Natalie Ward</v>
+        <v>Natalia Banas</v>
       </c>
       <c r="B545" t="str">
-        <v>wbinvs@gmail.com</v>
+        <v>info@nbaccommodation.co.uk</v>
       </c>
       <c r="C545" t="str">
-        <v>07828738479</v>
+        <v>07729919597</v>
       </c>
       <c r="D545" t="str">
-        <v/>
+        <v>NB Short Stay</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v xml:space="preserve">Natalie(WR6 6AE) Airbnb </v>
+        <v>Natalie Ward</v>
       </c>
       <c r="B546" t="str">
-        <v>nat@gmail.com</v>
+        <v>wbinvs@gmail.com</v>
       </c>
       <c r="C546" t="str">
-        <v>07892689525</v>
+        <v>07828738479</v>
       </c>
       <c r="D546" t="str">
         <v/>
@@ -28704,13 +28704,13 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Natasha</v>
+        <v xml:space="preserve">Natalie(WR6 6AE) Airbnb </v>
       </c>
       <c r="B547" t="str">
-        <v>natashacls.84@gmail.com</v>
+        <v>nat@gmail.com</v>
       </c>
       <c r="C547" t="str">
-        <v>07958 467558</v>
+        <v>07892689525</v>
       </c>
       <c r="D547" t="str">
         <v/>
@@ -28718,237 +28718,237 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Natasha Mcintosh | Mini Stay UK</v>
+        <v>Natasha</v>
       </c>
       <c r="B548" t="str">
-        <v>natasha@ministayuk.com</v>
+        <v>natashacls.84@gmail.com</v>
       </c>
       <c r="C548" t="str">
-        <v>07599163761</v>
+        <v>07958 467558</v>
       </c>
       <c r="D548" t="str">
-        <v>Mini Stay UK</v>
+        <v/>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Nathan Lamb</v>
+        <v>Natasha Mcintosh | Mini Stay UK</v>
       </c>
       <c r="B549" t="str">
-        <v>Betstaysltd@hotmail.com</v>
+        <v>natasha@ministayuk.com</v>
       </c>
       <c r="C549" t="str">
-        <v>07932092253</v>
+        <v>07599163761</v>
       </c>
       <c r="D549" t="str">
-        <v>Bet Estates</v>
+        <v>Mini Stay UK</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Necat Turan</v>
+        <v>Nathan Lamb</v>
       </c>
       <c r="B550" t="str">
-        <v>nijatt@hotmail.com</v>
+        <v>Betstaysltd@hotmail.com</v>
       </c>
       <c r="C550" t="str">
-        <v>07999326699</v>
+        <v>07932092253</v>
       </c>
       <c r="D550" t="str">
-        <v/>
+        <v>Bet Estates</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Neil</v>
+        <v>Necat Turan</v>
       </c>
       <c r="B551" t="str">
-        <v>info@smart-apartments.com</v>
+        <v>nijatt@hotmail.com</v>
       </c>
       <c r="C551" t="str">
-        <v>07749 471376</v>
+        <v>07999326699</v>
       </c>
       <c r="D551" t="str">
-        <v xml:space="preserve">Smart Apartments </v>
+        <v/>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Neil Withers</v>
+        <v>Neil</v>
       </c>
       <c r="B552" t="str">
-        <v>traceyjwg3@gmail.com</v>
+        <v>info@smart-apartments.com</v>
       </c>
       <c r="C552" t="str">
-        <v>+44 7915 252335</v>
+        <v>07749 471376</v>
       </c>
       <c r="D552" t="str">
-        <v/>
+        <v xml:space="preserve">Smart Apartments </v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Nev Memhet</v>
+        <v>Neil Withers</v>
       </c>
       <c r="B553" t="str">
-        <v>email@fkhdf.com</v>
+        <v>traceyjwg3@gmail.com</v>
       </c>
       <c r="C553" t="str">
-        <v>+447931576802</v>
+        <v>+44 7915 252335</v>
       </c>
       <c r="D553" t="str">
-        <v>https://ukstaysandexperiences.co.uk/</v>
+        <v/>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Nick Cham | Delight Marvel Properties</v>
+        <v>Nev Memhet</v>
       </c>
       <c r="B554" t="str">
-        <v>office@delightmarvel.com</v>
+        <v>email@fkhdf.com</v>
       </c>
       <c r="C554" t="str">
-        <v>07585244140</v>
+        <v>+447931576802</v>
       </c>
       <c r="D554" t="str">
-        <v>Delight Marvel Properties</v>
+        <v>https://ukstaysandexperiences.co.uk/</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Nicola | Foundry Farm / Sinclair Accommodations</v>
+        <v>Nick Cham | Delight Marvel Properties</v>
       </c>
       <c r="B555" t="str">
-        <v>nicola@foundryfarmholidays.com</v>
+        <v>office@delightmarvel.com</v>
       </c>
       <c r="C555" t="str">
-        <v>07432 202618</v>
+        <v>07585244140</v>
       </c>
       <c r="D555" t="str">
-        <v/>
+        <v>Delight Marvel Properties</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Nicole Jarrett Francis</v>
+        <v>Nicola | Foundry Farm / Sinclair Accommodations</v>
       </c>
       <c r="B556" t="str">
-        <v>info@prosperityrelocations.co.uk</v>
+        <v>nicola@foundryfarmholidays.com</v>
       </c>
       <c r="C556" t="str">
-        <v>07835 754 151</v>
+        <v>07432 202618</v>
       </c>
       <c r="D556" t="str">
-        <v>Prosperity Relocations</v>
+        <v/>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Nicole Noir</v>
+        <v>Nicole Jarrett Francis</v>
       </c>
       <c r="B557" t="str">
-        <v>info@laniorpropertygroup.com</v>
+        <v>info@prosperityrelocations.co.uk</v>
       </c>
       <c r="C557" t="str">
-        <v>07702589811</v>
+        <v>07835 754 151</v>
       </c>
       <c r="D557" t="str">
-        <v>laniorpropertygroup.com</v>
+        <v>Prosperity Relocations</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v xml:space="preserve">Nicole Noir </v>
+        <v>Nicole Noir</v>
       </c>
       <c r="B558" t="str">
-        <v>nottttreallllllllll@gmail.com</v>
+        <v>info@laniorpropertygroup.com</v>
       </c>
       <c r="C558" t="str">
         <v>07702589811</v>
       </c>
       <c r="D558" t="str">
-        <v/>
+        <v>laniorpropertygroup.com</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Nikki Naylor</v>
+        <v xml:space="preserve">Nicole Noir </v>
       </c>
       <c r="B559" t="str">
-        <v>nikki@lullabylettings.co.uk</v>
+        <v>nottttreallllllllll@gmail.com</v>
       </c>
       <c r="C559" t="str">
-        <v>07782972514</v>
+        <v>07702589811</v>
       </c>
       <c r="D559" t="str">
-        <v>Lullaby Lettings</v>
+        <v/>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Nina</v>
+        <v>Nikki Naylor</v>
       </c>
       <c r="B560" t="str">
-        <v>info@elitelettings.co</v>
+        <v>nikki@lullabylettings.co.uk</v>
       </c>
       <c r="C560" t="str">
-        <v>07766 330085</v>
+        <v>07782972514</v>
       </c>
       <c r="D560" t="str">
-        <v/>
+        <v>Lullaby Lettings</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Niro</v>
+        <v>Nina</v>
       </c>
       <c r="B561" t="str">
-        <v>contact@baldwinpg.com</v>
+        <v>info@elitelettings.co</v>
       </c>
       <c r="C561" t="str">
-        <v>07723 567414</v>
+        <v>07766 330085</v>
       </c>
       <c r="D561" t="str">
-        <v>BPG Serviced Accommodations</v>
+        <v/>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Noor | Sleepy Lodge</v>
+        <v>Niro</v>
       </c>
       <c r="B562" t="str">
-        <v>noor@email.com</v>
+        <v>contact@baldwinpg.com</v>
       </c>
       <c r="C562" t="str">
-        <v>07387564226</v>
+        <v>07723 567414</v>
       </c>
       <c r="D562" t="str">
-        <v>Sleepy Lodge</v>
+        <v>BPG Serviced Accommodations</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Normz Cozy Crib</v>
+        <v>Noor | Sleepy Lodge</v>
       </c>
       <c r="B563" t="str">
-        <v>normzcozycrib.sa@gmail.com</v>
+        <v>noor@email.com</v>
       </c>
       <c r="C563" t="str">
-        <v>07748 743004</v>
+        <v>07387564226</v>
       </c>
       <c r="D563" t="str">
-        <v/>
+        <v>Sleepy Lodge</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Nuovo Hotel Group</v>
+        <v>Normz Cozy Crib</v>
       </c>
       <c r="B564" t="str">
-        <v>nuovo@hotelgroup.co.uk</v>
+        <v>normzcozycrib.sa@gmail.com</v>
       </c>
       <c r="C564" t="str">
-        <v>0121 2812206</v>
+        <v>07748 743004</v>
       </c>
       <c r="D564" t="str">
         <v/>
@@ -28956,13 +28956,13 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Nurgul</v>
+        <v>Nuovo Hotel Group</v>
       </c>
       <c r="B565" t="str">
-        <v>setsproperties@gmail.com</v>
+        <v>nuovo@hotelgroup.co.uk</v>
       </c>
       <c r="C565" t="str">
-        <v>07871530800</v>
+        <v>0121 2812206</v>
       </c>
       <c r="D565" t="str">
         <v/>
@@ -28970,13 +28970,13 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Nwaego | Wego Homes</v>
+        <v>Nurgul</v>
       </c>
       <c r="B566" t="str">
-        <v>info@wegohomes.co.uk</v>
+        <v>setsproperties@gmail.com</v>
       </c>
       <c r="C566" t="str">
-        <v>07404793369</v>
+        <v>07871530800</v>
       </c>
       <c r="D566" t="str">
         <v/>
@@ -28984,97 +28984,97 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Nyema</v>
+        <v>Nwaego | Wego Homes</v>
       </c>
       <c r="B567" t="str">
-        <v>standoutnationalrelocations@gmail.com</v>
+        <v>info@wegohomes.co.uk</v>
       </c>
       <c r="C567" t="str">
-        <v>+448450606016</v>
+        <v>07404793369</v>
       </c>
       <c r="D567" t="str">
-        <v>Standout National Relocations</v>
+        <v/>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Olcier</v>
+        <v>Nyema</v>
       </c>
       <c r="B568" t="str">
-        <v>bookings@staylets.co.uk</v>
+        <v>standoutnationalrelocations@gmail.com</v>
       </c>
       <c r="C568" t="str">
-        <v>03301 075622</v>
+        <v>+448450606016</v>
       </c>
       <c r="D568" t="str">
-        <v>Stay Lets</v>
+        <v>Standout National Relocations</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Olivia</v>
+        <v>Olcier</v>
       </c>
       <c r="B569" t="str">
-        <v>info@avhughesproperties.com</v>
+        <v>bookings@staylets.co.uk</v>
       </c>
       <c r="C569" t="str">
-        <v>+447845 025 299</v>
+        <v>03301 075622</v>
       </c>
       <c r="D569" t="str">
-        <v>AV Hughes Properties</v>
+        <v>Stay Lets</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Olivia Sloan</v>
+        <v>Olivia</v>
       </c>
       <c r="B570" t="str">
-        <v>greencastleo@gmail.com</v>
+        <v>info@avhughesproperties.com</v>
       </c>
       <c r="C570" t="str">
-        <v>07927793796</v>
+        <v>+447845 025 299</v>
       </c>
       <c r="D570" t="str">
-        <v/>
+        <v>AV Hughes Properties</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Ollie Lang</v>
+        <v>Olivia Sloan</v>
       </c>
       <c r="B571" t="str">
-        <v>ollie@perfectbooking.co.uk</v>
+        <v>greencastleo@gmail.com</v>
       </c>
       <c r="C571" t="str">
-        <v>07826854682</v>
+        <v>07927793796</v>
       </c>
       <c r="D571" t="str">
-        <v>Perfect Booking</v>
+        <v/>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Ollie Whitehead</v>
+        <v>Ollie Lang</v>
       </c>
       <c r="B572" t="str">
-        <v>whiteheadmodelling12@gmail.com</v>
+        <v>ollie@perfectbooking.co.uk</v>
       </c>
       <c r="C572" t="str">
-        <v>+447552468437</v>
+        <v>07826854682</v>
       </c>
       <c r="D572" t="str">
-        <v/>
+        <v>Perfect Booking</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Omar</v>
+        <v>Ollie Whitehead</v>
       </c>
       <c r="B573" t="str">
-        <v>owner@simms-service-accommodation.co.uk</v>
+        <v>whiteheadmodelling12@gmail.com</v>
       </c>
       <c r="C573" t="str">
-        <v>7961327520</v>
+        <v>+447552468437</v>
       </c>
       <c r="D573" t="str">
         <v/>
@@ -29082,13 +29082,13 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Omotoyosi</v>
+        <v>Omar</v>
       </c>
       <c r="B574" t="str">
-        <v>dontknow1@c.com</v>
+        <v>owner@simms-service-accommodation.co.uk</v>
       </c>
       <c r="C574" t="str">
-        <v>+447835014422</v>
+        <v>7961327520</v>
       </c>
       <c r="D574" t="str">
         <v/>
@@ -29096,69 +29096,69 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>On Point Properties</v>
+        <v>Omotoyosi</v>
       </c>
       <c r="B575" t="str">
-        <v>info@onpointproperty.co.uk</v>
+        <v>dontknow1@c.com</v>
       </c>
       <c r="C575" t="str">
-        <v>020 37358977</v>
+        <v>+447835014422</v>
       </c>
       <c r="D575" t="str">
-        <v>airbnb</v>
+        <v/>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Open Mind Properties</v>
+        <v>On Point Properties</v>
       </c>
       <c r="B576" t="str">
-        <v>contact@openmindproperty.co.uk</v>
+        <v>info@onpointproperty.co.uk</v>
       </c>
       <c r="C576" t="str">
-        <v>020 3838 1825</v>
+        <v>020 37358977</v>
       </c>
       <c r="D576" t="str">
-        <v/>
+        <v>airbnb</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Orla &amp; Titti</v>
+        <v>Open Mind Properties</v>
       </c>
       <c r="B577" t="str">
-        <v>bookings@myhomeisyours.com</v>
+        <v>contact@openmindproperty.co.uk</v>
       </c>
       <c r="C577" t="str">
-        <v>0330 043 4566</v>
+        <v>020 3838 1825</v>
       </c>
       <c r="D577" t="str">
-        <v>myhomeisyours</v>
+        <v/>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Orla Carol</v>
+        <v>Orla &amp; Titti</v>
       </c>
       <c r="B578" t="str">
-        <v>office@mylivity.co.uk</v>
+        <v>bookings@myhomeisyours.com</v>
       </c>
       <c r="C578" t="str">
-        <v>07961 688628</v>
+        <v>0330 043 4566</v>
       </c>
       <c r="D578" t="str">
-        <v/>
+        <v>myhomeisyours</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Orla Dunne</v>
+        <v>Orla Carol</v>
       </c>
       <c r="B579" t="str">
-        <v>orla@myhomeisyours.com</v>
+        <v>office@mylivity.co.uk</v>
       </c>
       <c r="C579" t="str">
-        <v>07900817704</v>
+        <v>07961 688628</v>
       </c>
       <c r="D579" t="str">
         <v/>
@@ -29166,69 +29166,69 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Orlaith</v>
+        <v>Orla Dunne</v>
       </c>
       <c r="B580" t="str">
-        <v>hello@escapesandestates.co.uk</v>
+        <v>orla@myhomeisyours.com</v>
       </c>
       <c r="C580" t="str">
-        <v>07392 520042</v>
+        <v>07900817704</v>
       </c>
       <c r="D580" t="str">
-        <v>Escapes &amp; Estates</v>
+        <v/>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Osborn Leisure</v>
+        <v>Orlaith</v>
       </c>
       <c r="B581" t="str">
-        <v>team@osborngroup.co.uk</v>
+        <v>hello@escapesandestates.co.uk</v>
       </c>
       <c r="C581" t="str">
-        <v>01825 732617</v>
+        <v>07392 520042</v>
       </c>
       <c r="D581" t="str">
-        <v/>
+        <v>Escapes &amp; Estates</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Ozzy</v>
+        <v>Osborn Leisure</v>
       </c>
       <c r="B582" t="str">
-        <v>hello@bookmyplace.co.uk</v>
+        <v>team@osborngroup.co.uk</v>
       </c>
       <c r="C582" t="str">
-        <v>07702874035</v>
+        <v>01825 732617</v>
       </c>
       <c r="D582" t="str">
-        <v>Book My Place</v>
+        <v/>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pam Nash</v>
+        <v>Ozzy</v>
       </c>
       <c r="B583" t="str">
-        <v>itisreal.net@gmail.com</v>
+        <v>hello@bookmyplace.co.uk</v>
       </c>
       <c r="C583" t="str">
-        <v>07399153138</v>
+        <v>07702874035</v>
       </c>
       <c r="D583" t="str">
-        <v/>
+        <v>Book My Place</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Parshan Book My Digs</v>
+        <v>Pam Nash</v>
       </c>
       <c r="B584" t="str">
-        <v>letsdoit@bookmydigs.com</v>
+        <v>itisreal.net@gmail.com</v>
       </c>
       <c r="C584" t="str">
-        <v xml:space="preserve"> 0333 404 9215</v>
+        <v>07399153138</v>
       </c>
       <c r="D584" t="str">
         <v/>
@@ -29236,13 +29236,13 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Pass The Property</v>
+        <v>Parshan Book My Digs</v>
       </c>
       <c r="B585" t="str">
-        <v>info@passtheproperty.co.uk</v>
+        <v>letsdoit@bookmydigs.com</v>
       </c>
       <c r="C585" t="str">
-        <v>0333 301 0787</v>
+        <v xml:space="preserve"> 0333 404 9215</v>
       </c>
       <c r="D585" t="str">
         <v/>
@@ -29250,41 +29250,41 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Pass the Property</v>
+        <v>Pass The Property</v>
       </c>
       <c r="B586" t="str">
-        <v>bookings@passtheproperty.co.uk</v>
+        <v>info@passtheproperty.co.uk</v>
       </c>
       <c r="C586" t="str">
-        <v>0333 3010787</v>
+        <v>0333 301 0787</v>
       </c>
       <c r="D586" t="str">
-        <v>Pass The Property</v>
+        <v/>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Patsy restassuredproperties</v>
+        <v>Pass the Property</v>
       </c>
       <c r="B587" t="str">
-        <v>enquiries@restassuredproperties.co.uk</v>
+        <v>bookings@passtheproperty.co.uk</v>
       </c>
       <c r="C587" t="str">
-        <v>07722 294060</v>
+        <v>0333 3010787</v>
       </c>
       <c r="D587" t="str">
-        <v/>
+        <v>Pass The Property</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Paul</v>
+        <v>Patsy restassuredproperties</v>
       </c>
       <c r="B588" t="str">
-        <v>tom@polarproperties.co.uk</v>
+        <v>enquiries@restassuredproperties.co.uk</v>
       </c>
       <c r="C588" t="str">
-        <v>07585542067</v>
+        <v>07722 294060</v>
       </c>
       <c r="D588" t="str">
         <v/>
@@ -29295,13 +29295,13 @@
         <v>Paul</v>
       </c>
       <c r="B589" t="str">
-        <v>test@gmail.com</v>
+        <v>tom@polarproperties.co.uk</v>
       </c>
       <c r="C589" t="str">
-        <v>07411730504</v>
+        <v>07585542067</v>
       </c>
       <c r="D589" t="str">
-        <v>Ping Properties Ltd</v>
+        <v/>
       </c>
     </row>
     <row r="590">
@@ -29337,24 +29337,24 @@
         <v>Paul</v>
       </c>
       <c r="B592" t="str">
-        <v>paulsouthampton@gmail.com</v>
+        <v>test@gmail.com</v>
       </c>
       <c r="C592" t="str">
         <v>07411730504</v>
       </c>
       <c r="D592" t="str">
-        <v/>
+        <v>Ping Properties Ltd</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Paul Agbazaeze</v>
+        <v>Paul</v>
       </c>
       <c r="B593" t="str">
-        <v>info@sublime-stays.com</v>
+        <v>paulsouthampton@gmail.com</v>
       </c>
       <c r="C593" t="str">
-        <v>+63 935 508 4365</v>
+        <v>07411730504</v>
       </c>
       <c r="D593" t="str">
         <v/>
@@ -29362,7 +29362,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Paul Agbazaeze | Sublime</v>
+        <v>Paul Agbazaeze</v>
       </c>
       <c r="B594" t="str">
         <v>info@sublime-stays.com</v>
@@ -29376,69 +29376,69 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Paul and Malin</v>
+        <v>Paul Agbazaeze | Sublime</v>
       </c>
       <c r="B595" t="str">
-        <v>info@paulandmalin.com</v>
+        <v>info@sublime-stays.com</v>
       </c>
       <c r="C595" t="str">
-        <v>+44 7514 125653</v>
+        <v>+63 935 508 4365</v>
       </c>
       <c r="D595" t="str">
-        <v>Paul and Malin Properties LTD</v>
+        <v/>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Paulina Sliwa</v>
+        <v>Paul and Malin</v>
       </c>
       <c r="B596" t="str">
-        <v>info@londexap.com</v>
+        <v>info@paulandmalin.com</v>
       </c>
       <c r="C596" t="str">
-        <v>+448008886867</v>
+        <v>+44 7514 125653</v>
       </c>
       <c r="D596" t="str">
-        <v>London Executive Apartments</v>
+        <v>Paul and Malin Properties LTD</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v xml:space="preserve">Pegin Poulose </v>
+        <v>Paulina Sliwa</v>
       </c>
       <c r="B597" t="str">
-        <v>info@apexquarters.co.uk</v>
+        <v>info@londexap.com</v>
       </c>
       <c r="C597" t="str">
-        <v>07847327503</v>
+        <v>+448008886867</v>
       </c>
       <c r="D597" t="str">
-        <v>Apex Quaters</v>
+        <v>London Executive Apartments</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Pejman/Tiffany</v>
+        <v xml:space="preserve">Pegin Poulose </v>
       </c>
       <c r="B598" t="str">
-        <v>happyholidayhomesw9@gmail.com</v>
+        <v>info@apexquarters.co.uk</v>
       </c>
       <c r="C598" t="str">
-        <v>+44 7548 382023</v>
+        <v>07847327503</v>
       </c>
       <c r="D598" t="str">
-        <v/>
+        <v>Apex Quaters</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Peter Firth</v>
+        <v>Pejman/Tiffany</v>
       </c>
       <c r="B599" t="str">
-        <v>dont@mail.com</v>
+        <v>happyholidayhomesw9@gmail.com</v>
       </c>
       <c r="C599" t="str">
-        <v>+447859806867</v>
+        <v>+44 7548 382023</v>
       </c>
       <c r="D599" t="str">
         <v/>
@@ -29446,41 +29446,41 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Peter Solomon</v>
+        <v>Peter Firth</v>
       </c>
       <c r="B600" t="str">
-        <v>info@northsidepropertygroup.co.uk</v>
+        <v>dont@mail.com</v>
       </c>
       <c r="C600" t="str">
-        <v>07549 1975516</v>
+        <v>+447859806867</v>
       </c>
       <c r="D600" t="str">
-        <v>Northside Property Group</v>
+        <v/>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Phil | Airbnb</v>
+        <v>Peter Solomon</v>
       </c>
       <c r="B601" t="str">
-        <v>phil@yahoo.com</v>
+        <v>info@northsidepropertygroup.co.uk</v>
       </c>
       <c r="C601" t="str">
-        <v>123456789</v>
+        <v>07549 1975516</v>
       </c>
       <c r="D601" t="str">
-        <v/>
+        <v>Northside Property Group</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Phillipa (and Tim)</v>
+        <v>Phil | Airbnb</v>
       </c>
       <c r="B602" t="str">
-        <v>fake@email.com</v>
+        <v>phil@yahoo.com</v>
       </c>
       <c r="C602" t="str">
-        <v>07305021037</v>
+        <v>123456789</v>
       </c>
       <c r="D602" t="str">
         <v/>
@@ -29488,111 +29488,111 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Phyl Jennings</v>
+        <v>Phillipa (and Tim)</v>
       </c>
       <c r="B603" t="str">
-        <v>info@weareedens.com</v>
+        <v>fake@email.com</v>
       </c>
       <c r="C603" t="str">
-        <v>07480890959</v>
+        <v>07305021037</v>
       </c>
       <c r="D603" t="str">
-        <v>We Are Edens</v>
+        <v/>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Plamena</v>
+        <v>Phyl Jennings</v>
       </c>
       <c r="B604" t="str">
-        <v>manage@lettsgetsmart.com</v>
+        <v>info@weareedens.com</v>
       </c>
       <c r="C604" t="str">
-        <v>07414 549781</v>
+        <v>07480890959</v>
       </c>
       <c r="D604" t="str">
-        <v>lettsgetsmart</v>
+        <v>We Are Edens</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Polka Group</v>
+        <v>Plamena</v>
       </c>
       <c r="B605" t="str">
-        <v>support@polkagroup.co.uk</v>
+        <v>manage@lettsgetsmart.com</v>
       </c>
       <c r="C605" t="str">
-        <v>+44 7958 968029</v>
+        <v>07414 549781</v>
       </c>
       <c r="D605" t="str">
-        <v/>
+        <v>lettsgetsmart</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Prescott Apartments</v>
+        <v>Polka Group</v>
       </c>
       <c r="B606" t="str">
-        <v>stay@prescottapartments.co.uk</v>
+        <v>support@polkagroup.co.uk</v>
       </c>
       <c r="C606" t="str">
-        <v>03330 903529</v>
+        <v>+44 7958 968029</v>
       </c>
       <c r="D606" t="str">
-        <v>Prescott Serviced Apartments</v>
+        <v/>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Prince</v>
+        <v>Prescott Apartments</v>
       </c>
       <c r="B607" t="str">
-        <v>dontknow@don.com</v>
+        <v>stay@prescottapartments.co.uk</v>
       </c>
       <c r="C607" t="str">
-        <v>07988463377</v>
+        <v>03330 903529</v>
       </c>
       <c r="D607" t="str">
-        <v/>
+        <v>Prescott Serviced Apartments</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Prince Appiah</v>
+        <v>Prince</v>
       </c>
       <c r="B608" t="str">
-        <v>hello@iconlivingproperties.com</v>
+        <v>dontknow@don.com</v>
       </c>
       <c r="C608" t="str">
-        <v>07949637425</v>
+        <v>07988463377</v>
       </c>
       <c r="D608" t="str">
-        <v>Icon Living Properties Short Lets And Serviced Accommodation</v>
+        <v/>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Princes Street Suites</v>
+        <v>Prince Appiah</v>
       </c>
       <c r="B609" t="str">
-        <v>reception@princesstreetsuites.com</v>
+        <v>hello@iconlivingproperties.com</v>
       </c>
       <c r="C609" t="str">
-        <v>+44 (0)131 558 1600</v>
+        <v>07949637425</v>
       </c>
       <c r="D609" t="str">
-        <v/>
+        <v>Icon Living Properties Short Lets And Serviced Accommodation</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Principal Apartments</v>
+        <v>Princes Street Suites</v>
       </c>
       <c r="B610" t="str">
-        <v>enquiries@principalapartments.com</v>
+        <v>reception@princesstreetsuites.com</v>
       </c>
       <c r="C610" t="str">
-        <v>01414040086</v>
+        <v>+44 (0)131 558 1600</v>
       </c>
       <c r="D610" t="str">
         <v/>
@@ -29600,41 +29600,41 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Priya Chauhan</v>
+        <v>Principal Apartments</v>
       </c>
       <c r="B611" t="str">
-        <v>admin@ariapartments.com</v>
+        <v>enquiries@principalapartments.com</v>
       </c>
       <c r="C611" t="str">
-        <v>+44 333 444 1238</v>
+        <v>01414040086</v>
       </c>
       <c r="D611" t="str">
-        <v>Lyter Living Serviced Apartments</v>
+        <v/>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Property By Capital</v>
+        <v>Priya Chauhan</v>
       </c>
       <c r="B612" t="str">
-        <v>reservations@propertybycapital.com</v>
+        <v>admin@ariapartments.com</v>
       </c>
       <c r="C612" t="str">
-        <v>0203 740 4160</v>
+        <v>+44 333 444 1238</v>
       </c>
       <c r="D612" t="str">
-        <v/>
+        <v>Lyter Living Serviced Apartments</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Pui</v>
+        <v>Property By Capital</v>
       </c>
       <c r="B613" t="str">
-        <v>info@mustardseedestate.co.uk</v>
+        <v>reservations@propertybycapital.com</v>
       </c>
       <c r="C613" t="str">
-        <v xml:space="preserve"> 07858 566096</v>
+        <v>0203 740 4160</v>
       </c>
       <c r="D613" t="str">
         <v/>
@@ -29642,55 +29642,55 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pure Serviced</v>
+        <v>Pui</v>
       </c>
       <c r="B614" t="str">
-        <v>hello@pureserviced.com</v>
+        <v>info@mustardseedestate.co.uk</v>
       </c>
       <c r="C614" t="str">
-        <v>01752 426428</v>
+        <v xml:space="preserve"> 07858 566096</v>
       </c>
       <c r="D614" t="str">
-        <v>Pure Serviced</v>
+        <v/>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Quay Holidays</v>
+        <v>Pure Serviced</v>
       </c>
       <c r="B615" t="str">
-        <v>stay@quayholidays.co.uk</v>
+        <v>hello@pureserviced.com</v>
       </c>
       <c r="C615" t="str">
-        <v>01202683333</v>
+        <v>01752 426428</v>
       </c>
       <c r="D615" t="str">
-        <v>Quay Holiday</v>
+        <v>Pure Serviced</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Queen Street Aparthotel</v>
+        <v>Quay Holidays</v>
       </c>
       <c r="B616" t="str">
-        <v>fake@queenstreet.com</v>
+        <v>stay@quayholidays.co.uk</v>
       </c>
       <c r="C616" t="str">
-        <v>0000000000</v>
+        <v>01202683333</v>
       </c>
       <c r="D616" t="str">
-        <v/>
+        <v>Quay Holiday</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Rachael Walker</v>
+        <v>Queen Street Aparthotel</v>
       </c>
       <c r="B617" t="str">
-        <v>rachael@wehostchester.uk</v>
+        <v>fake@queenstreet.com</v>
       </c>
       <c r="C617" t="str">
-        <v>+44 7388 346975</v>
+        <v>0000000000</v>
       </c>
       <c r="D617" t="str">
         <v/>
@@ -29698,13 +29698,13 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Rachel</v>
+        <v xml:space="preserve">Quins Place </v>
       </c>
       <c r="B618" t="str">
-        <v>enquiries@solentretreat.com</v>
+        <v>Info@quinsplace.co.uk</v>
       </c>
       <c r="C618" t="str">
-        <v>07841 319519</v>
+        <v>07447675154</v>
       </c>
       <c r="D618" t="str">
         <v/>
@@ -29712,27 +29712,27 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Rachel Lowe</v>
+        <v>Rachael Walker</v>
       </c>
       <c r="B619" t="str">
-        <v>info@eshostays.com</v>
+        <v>rachael@wehostchester.uk</v>
       </c>
       <c r="C619" t="str">
-        <v>01452 903703</v>
+        <v>+44 7388 346975</v>
       </c>
       <c r="D619" t="str">
-        <v>esho stays</v>
+        <v/>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Rachel Watkin</v>
+        <v>Rachel</v>
       </c>
       <c r="B620" t="str">
-        <v>rachel@rachelwatkin.com</v>
+        <v>enquiries@solentretreat.com</v>
       </c>
       <c r="C620" t="str">
-        <v>+44 7757 389540</v>
+        <v>07841 319519</v>
       </c>
       <c r="D620" t="str">
         <v/>
@@ -29740,27 +29740,27 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Rae Managible</v>
+        <v>Rachel Lowe</v>
       </c>
       <c r="B621" t="str">
-        <v>fake@emmmmail.com</v>
+        <v>info@eshostays.com</v>
       </c>
       <c r="C621" t="str">
-        <v>07882209236</v>
+        <v>01452 903703</v>
       </c>
       <c r="D621" t="str">
-        <v/>
+        <v>esho stays</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Rahul</v>
+        <v>Rachel Watkin</v>
       </c>
       <c r="B622" t="str">
-        <v>stay@thesqua.re.re</v>
+        <v>rachel@rachelwatkin.com</v>
       </c>
       <c r="C622" t="str">
-        <v>07701 410160</v>
+        <v>+44 7757 389540</v>
       </c>
       <c r="D622" t="str">
         <v/>
@@ -29768,69 +29768,69 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Rahul</v>
+        <v>Rae Managible</v>
       </c>
       <c r="B623" t="str">
-        <v>hello@elite-stays.co.uk</v>
+        <v>fake@emmmmail.com</v>
       </c>
       <c r="C623" t="str">
-        <v>01135344412</v>
+        <v>07882209236</v>
       </c>
       <c r="D623" t="str">
-        <v>Elite Stays</v>
+        <v/>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Rahul Kumar</v>
+        <v>Rahul</v>
       </c>
       <c r="B624" t="str">
-        <v>stay@thesqua.re</v>
+        <v>stay@thesqua.re.re</v>
       </c>
       <c r="C624" t="str">
-        <v xml:space="preserve">44 (0) 7701410 160 </v>
+        <v>07701 410160</v>
       </c>
       <c r="D624" t="str">
-        <v>squa.re</v>
+        <v/>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Raj</v>
+        <v>Rahul</v>
       </c>
       <c r="B625" t="str">
-        <v>rajk2022x@gmail.com</v>
+        <v>hello@elite-stays.co.uk</v>
       </c>
       <c r="C625" t="str">
-        <v>+447951005052</v>
+        <v>01135344412</v>
       </c>
       <c r="D625" t="str">
-        <v/>
+        <v>Elite Stays</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Rajan Singh Kalsi</v>
+        <v>Rahul Kumar</v>
       </c>
       <c r="B626" t="str">
-        <v>rajan@kinara-properties.com</v>
+        <v>stay@thesqua.re</v>
       </c>
       <c r="C626" t="str">
-        <v>07854 599 920</v>
+        <v xml:space="preserve">44 (0) 7701410 160 </v>
       </c>
       <c r="D626" t="str">
-        <v/>
+        <v>squa.re</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Raluca Olteanu</v>
+        <v>Raj</v>
       </c>
       <c r="B627" t="str">
-        <v>raluca@amprentaproperties.co.uk</v>
+        <v>rajk2022x@gmail.com</v>
       </c>
       <c r="C627" t="str">
-        <v>07726454427</v>
+        <v>+447951005052</v>
       </c>
       <c r="D627" t="str">
         <v/>
@@ -29838,13 +29838,13 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Rasheed</v>
+        <v>Rajan Singh Kalsi</v>
       </c>
       <c r="B628" t="str">
-        <v>rasheed@Fake.com</v>
+        <v>rajan@kinara-properties.com</v>
       </c>
       <c r="C628" t="str">
-        <v>+44 7445 207197</v>
+        <v>07854 599 920</v>
       </c>
       <c r="D628" t="str">
         <v/>
@@ -29852,69 +29852,69 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Rashid</v>
+        <v>Raluca Olteanu</v>
       </c>
       <c r="B629" t="str">
-        <v>q@propertyy.io</v>
+        <v>raluca@amprentaproperties.co.uk</v>
       </c>
       <c r="C629" t="str">
-        <v>0000000000</v>
+        <v>07726454427</v>
       </c>
       <c r="D629" t="str">
-        <v>Propertyy.io</v>
+        <v/>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Raul</v>
+        <v>Rasheed</v>
       </c>
       <c r="B630" t="str">
-        <v>info@ideallyproperties.com</v>
+        <v>rasheed@Fake.com</v>
       </c>
       <c r="C630" t="str">
-        <v>07882026845</v>
+        <v>+44 7445 207197</v>
       </c>
       <c r="D630" t="str">
-        <v>ideallyproperties.com</v>
+        <v/>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Rav</v>
+        <v>Rashid</v>
       </c>
       <c r="B631" t="str">
-        <v>rav@kayloproperty.co.uk</v>
+        <v>q@propertyy.io</v>
       </c>
       <c r="C631" t="str">
-        <v>+447958084066</v>
+        <v>0000000000</v>
       </c>
       <c r="D631" t="str">
-        <v/>
+        <v>Propertyy.io</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Ray</v>
+        <v>Raul</v>
       </c>
       <c r="B632" t="str">
-        <v>hazelcozyhomes@yahoo.com</v>
+        <v>info@ideallyproperties.com</v>
       </c>
       <c r="C632" t="str">
-        <v>+447861668787</v>
+        <v>07882026845</v>
       </c>
       <c r="D632" t="str">
-        <v>HazelCozyhomes</v>
+        <v>ideallyproperties.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v xml:space="preserve">Razia </v>
+        <v>Rav</v>
       </c>
       <c r="B633" t="str">
-        <v>sdfghj@df.com</v>
+        <v>rav@kayloproperty.co.uk</v>
       </c>
       <c r="C633" t="str">
-        <v>07787987661</v>
+        <v>+447958084066</v>
       </c>
       <c r="D633" t="str">
         <v/>
@@ -29922,125 +29922,125 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Rebecca Hannis</v>
+        <v>Ray</v>
       </c>
       <c r="B634" t="str">
-        <v>rebeccahannis@yahoo.co.uk</v>
+        <v>hazelcozyhomes@yahoo.com</v>
       </c>
       <c r="C634" t="str">
-        <v>7971713382</v>
+        <v>+447861668787</v>
       </c>
       <c r="D634" t="str">
-        <v/>
+        <v>HazelCozyhomes</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Rebecca Li</v>
+        <v xml:space="preserve">Razia </v>
       </c>
       <c r="B635" t="str">
-        <v>beestayltd@gmail.com</v>
+        <v>sdfghj@df.com</v>
       </c>
       <c r="C635" t="str">
-        <v>+447546527758</v>
+        <v>07787987661</v>
       </c>
       <c r="D635" t="str">
-        <v>Bee stay</v>
+        <v/>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Reine</v>
+        <v>Rebecca Hannis</v>
       </c>
       <c r="B636" t="str">
-        <v>contact@theobuasproperties.com</v>
+        <v>rebeccahannis@yahoo.co.uk</v>
       </c>
       <c r="C636" t="str">
-        <v>07469 188424</v>
+        <v>7971713382</v>
       </c>
       <c r="D636" t="str">
-        <v xml:space="preserve"> Obuas Properties</v>
+        <v/>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Remi</v>
+        <v>Rebecca Li</v>
       </c>
       <c r="B637" t="str">
-        <v>FAKRE@DL.COM</v>
+        <v>beestayltd@gmail.com</v>
       </c>
       <c r="C637" t="str">
-        <v>07947 959396</v>
+        <v>+447546527758</v>
       </c>
       <c r="D637" t="str">
-        <v>DELUSH</v>
+        <v>Bee stay</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v xml:space="preserve">Residence Inn </v>
+        <v>Reine</v>
       </c>
       <c r="B638" t="str">
-        <v>reception@residenceinnmanchesterpiccadilly.com</v>
+        <v>contact@theobuasproperties.com</v>
       </c>
       <c r="C638" t="str">
-        <v>01618417800</v>
+        <v>07469 188424</v>
       </c>
       <c r="D638" t="str">
-        <v>https://www.marriott.com/en-us/hotels/manri-residence-inn-manchester-piccadilly/overview/</v>
+        <v xml:space="preserve"> Obuas Properties</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Rhiane</v>
+        <v>Remi</v>
       </c>
       <c r="B639" t="str">
-        <v>fullhousepropertygroup@gmail.com</v>
+        <v>FAKRE@DL.COM</v>
       </c>
       <c r="C639" t="str">
-        <v>03333355203</v>
+        <v>07947 959396</v>
       </c>
       <c r="D639" t="str">
-        <v>fullhousepropertygroup</v>
+        <v>DELUSH</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Rhianna</v>
+        <v xml:space="preserve">Residence Inn </v>
       </c>
       <c r="B640" t="str">
-        <v>info@lgwshortlets.co.uk</v>
+        <v>reception@residenceinnmanchesterpiccadilly.com</v>
       </c>
       <c r="C640" t="str">
-        <v>07919405302</v>
+        <v>01618417800</v>
       </c>
       <c r="D640" t="str">
-        <v/>
+        <v>https://www.marriott.com/en-us/hotels/manri-residence-inn-manchester-piccadilly/overview/</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Richard</v>
+        <v>Rhiane</v>
       </c>
       <c r="B641" t="str">
-        <v>info@rdcshortstays.co.uk</v>
+        <v>fullhousepropertygroup@gmail.com</v>
       </c>
       <c r="C641" t="str">
-        <v>07714235129</v>
+        <v>03333355203</v>
       </c>
       <c r="D641" t="str">
-        <v>rdcshortstays.co.uk</v>
+        <v>fullhousepropertygroup</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Richard Adiole</v>
+        <v>Rhianna</v>
       </c>
       <c r="B642" t="str">
-        <v>fake@airbnb.com</v>
+        <v>info@lgwshortlets.co.uk</v>
       </c>
       <c r="C642" t="str">
-        <v>+447928478400</v>
+        <v>07919405302</v>
       </c>
       <c r="D642" t="str">
         <v/>
@@ -30048,153 +30048,153 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Richard Adiole</v>
+        <v>Richard</v>
       </c>
       <c r="B643" t="str">
-        <v>richard@fake.com</v>
+        <v>info@rdcshortstays.co.uk</v>
       </c>
       <c r="C643" t="str">
-        <v>07928478400</v>
+        <v>07714235129</v>
       </c>
       <c r="D643" t="str">
-        <v/>
+        <v>rdcshortstays.co.uk</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Richard Applegate</v>
+        <v>Richard Adiole</v>
       </c>
       <c r="B644" t="str">
-        <v>info@thecosycorner.co.uk</v>
+        <v>fake@airbnb.com</v>
       </c>
       <c r="C644" t="str">
-        <v>07411 534024</v>
+        <v>+447928478400</v>
       </c>
       <c r="D644" t="str">
-        <v>The Cosy Corner</v>
+        <v/>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Richard Bennie</v>
+        <v>Richard Adiole</v>
       </c>
       <c r="B645" t="str">
-        <v>tbcASK@greensandoaks.co.uk</v>
+        <v>richard@fake.com</v>
       </c>
       <c r="C645" t="str">
-        <v>07766 452834</v>
+        <v>07928478400</v>
       </c>
       <c r="D645" t="str">
-        <v>greensandoaks.co.uk</v>
+        <v/>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Richard Bowyer</v>
+        <v>Richard Applegate</v>
       </c>
       <c r="B646" t="str">
-        <v>richard@bowpropertyltd.com</v>
+        <v>info@thecosycorner.co.uk</v>
       </c>
       <c r="C646" t="str">
-        <v>07710141856</v>
+        <v>07411 534024</v>
       </c>
       <c r="D646" t="str">
-        <v>Bow Property Ltd</v>
+        <v>The Cosy Corner</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v xml:space="preserve">Richard Haggerty </v>
+        <v>Richard Bennie</v>
       </c>
       <c r="B647" t="str">
-        <v>richard@guestinourhouse.co.uk</v>
+        <v>tbcASK@greensandoaks.co.uk</v>
       </c>
       <c r="C647" t="str">
-        <v>07790822603</v>
+        <v>07766 452834</v>
       </c>
       <c r="D647" t="str">
-        <v/>
+        <v>greensandoaks.co.uk</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Richard Manetta</v>
+        <v>Richard Bowyer</v>
       </c>
       <c r="B648" t="str">
-        <v>richard@gmail.com</v>
+        <v>richard@bowpropertyltd.com</v>
       </c>
       <c r="C648" t="str">
-        <v>07950 267574</v>
+        <v>07710141856</v>
       </c>
       <c r="D648" t="str">
-        <v/>
+        <v>Bow Property Ltd</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Richard Wylde</v>
+        <v xml:space="preserve">Richard Haggerty </v>
       </c>
       <c r="B649" t="str">
-        <v>booking@whiskawaystays.com</v>
+        <v>richard@guestinourhouse.co.uk</v>
       </c>
       <c r="C649" t="str">
-        <v>01905671468</v>
+        <v>07790822603</v>
       </c>
       <c r="D649" t="str">
-        <v>Whisk Away Stays</v>
+        <v/>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Ridouen</v>
+        <v>Richard Manetta</v>
       </c>
       <c r="B650" t="str">
-        <v>123@airbnb.com</v>
+        <v>richard@gmail.com</v>
       </c>
       <c r="C650" t="str">
-        <v>+8801612944000</v>
+        <v>07950 267574</v>
       </c>
       <c r="D650" t="str">
-        <v>Live London</v>
+        <v/>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Righ Properties</v>
+        <v>Richard Wylde</v>
       </c>
       <c r="B651" t="str">
-        <v>reservations@righproperties.com</v>
+        <v>booking@whiskawaystays.com</v>
       </c>
       <c r="C651" t="str">
-        <v>0131 5634229</v>
+        <v>01905671468</v>
       </c>
       <c r="D651" t="str">
-        <v/>
+        <v>Whisk Away Stays</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Riize Rooms</v>
+        <v>Ridouen</v>
       </c>
       <c r="B652" t="str">
-        <v>hello@riize.co.uk</v>
+        <v>123@airbnb.com</v>
       </c>
       <c r="C652" t="str">
-        <v>01905972578</v>
+        <v>+8801612944000</v>
       </c>
       <c r="D652" t="str">
-        <v/>
+        <v>Live London</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Rithick | Hyped Property</v>
+        <v>Righ Properties</v>
       </c>
       <c r="B653" t="str">
-        <v>info@hyped-properties.co.uk</v>
+        <v>reservations@righproperties.com</v>
       </c>
       <c r="C653" t="str">
-        <v>07447779996</v>
+        <v>0131 5634229</v>
       </c>
       <c r="D653" t="str">
         <v/>
@@ -30202,97 +30202,97 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Rizwana</v>
+        <v>Riize Rooms</v>
       </c>
       <c r="B654" t="str">
-        <v>hello@maxandmashomes.com</v>
+        <v>hello@riize.co.uk</v>
       </c>
       <c r="C654" t="str">
-        <v>07356029516</v>
+        <v>01905972578</v>
       </c>
       <c r="D654" t="str">
-        <v>https://www.maxandmashomes.com/book-here</v>
+        <v/>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Rob &amp; Chris</v>
+        <v>Rithick | Hyped Property</v>
       </c>
       <c r="B655" t="str">
-        <v>info@prime-ps.co.uk</v>
+        <v>info@hyped-properties.co.uk</v>
       </c>
       <c r="C655" t="str">
-        <v>07935 180652</v>
+        <v>07447779996</v>
       </c>
       <c r="D655" t="str">
-        <v>Prime Property Solution</v>
+        <v/>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Rob &amp; Sue</v>
+        <v>Rizwana</v>
       </c>
       <c r="B656" t="str">
-        <v>maidenheadshortstay@gmail.com</v>
+        <v>hello@maxandmashomes.com</v>
       </c>
       <c r="C656" t="str">
-        <v>+44 7955 750639</v>
+        <v>07356029516</v>
       </c>
       <c r="D656" t="str">
-        <v>https://maidenheadshortstay.com/24-medway-house/</v>
+        <v>https://www.maxandmashomes.com/book-here</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Rob Mears</v>
+        <v>Rob &amp; Chris</v>
       </c>
       <c r="B657" t="str">
-        <v>info@awaystays.co.uk</v>
+        <v>info@prime-ps.co.uk</v>
       </c>
       <c r="C657" t="str">
-        <v>0333 772 1799</v>
+        <v>07935 180652</v>
       </c>
       <c r="D657" t="str">
-        <v>Away Stays</v>
+        <v>Prime Property Solution</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Romina aibnb</v>
+        <v>Rob &amp; Sue</v>
       </c>
       <c r="B658" t="str">
-        <v>romina@gmaol.com</v>
+        <v>maidenheadshortstay@gmail.com</v>
       </c>
       <c r="C658" t="str">
-        <v>1233456789</v>
+        <v>+44 7955 750639</v>
       </c>
       <c r="D658" t="str">
-        <v/>
+        <v>https://maidenheadshortstay.com/24-medway-house/</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Ronnie Robinson</v>
+        <v>Rob Mears</v>
       </c>
       <c r="B659" t="str">
-        <v>info@randrproperties.co.uk</v>
+        <v>info@awaystays.co.uk</v>
       </c>
       <c r="C659" t="str">
-        <v>01902 934135</v>
+        <v>0333 772 1799</v>
       </c>
       <c r="D659" t="str">
-        <v>randrproperties</v>
+        <v>Away Stays</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Rory Gray</v>
+        <v>Romina aibnb</v>
       </c>
       <c r="B660" t="str">
-        <v>rory@marketmyproperty.co</v>
+        <v>romina@gmaol.com</v>
       </c>
       <c r="C660" t="str">
-        <v>07426850493</v>
+        <v>1233456789</v>
       </c>
       <c r="D660" t="str">
         <v/>
@@ -30300,27 +30300,27 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Rose</v>
+        <v>Ronnie Robinson</v>
       </c>
       <c r="B661" t="str">
-        <v>rvdreamhomes@yahoo.com</v>
+        <v>info@randrproperties.co.uk</v>
       </c>
       <c r="C661" t="str">
-        <v>+447877 073364</v>
+        <v>01902 934135</v>
       </c>
       <c r="D661" t="str">
-        <v>https://www.rosevillhomes.com/room/self-contained-loft-annex?info%5Barrival_date%5D=24%2F09%2F2024&amp;info%5Bdeparture_date%5D=26%2F09%2F2024&amp;info%5Brooms%5D=true&amp;info%5Btotal_adult%5D=2</v>
+        <v>randrproperties</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Rose Platinum Properties</v>
+        <v>Rory Gray</v>
       </c>
       <c r="B662" t="str">
-        <v>rtu@tyui.com</v>
+        <v>rory@marketmyproperty.co</v>
       </c>
       <c r="C662" t="str">
-        <v>07440579926</v>
+        <v>07426850493</v>
       </c>
       <c r="D662" t="str">
         <v/>
@@ -30328,41 +30328,41 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Rosemary Ni Sassi</v>
+        <v>Rose</v>
       </c>
       <c r="B663" t="str">
-        <v>rns@Qapartments.com</v>
+        <v>rvdreamhomes@yahoo.com</v>
       </c>
       <c r="C663" t="str">
-        <v>+44 20 3404 4040</v>
+        <v>+447877 073364</v>
       </c>
       <c r="D663" t="str">
-        <v/>
+        <v>https://www.rosevillhomes.com/room/self-contained-loft-annex?info%5Barrival_date%5D=24%2F09%2F2024&amp;info%5Bdeparture_date%5D=26%2F09%2F2024&amp;info%5Brooms%5D=true&amp;info%5Btotal_adult%5D=2</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Rosie (REO Homes)</v>
+        <v>Rose Platinum Properties</v>
       </c>
       <c r="B664" t="str">
-        <v>info@reohomes.co.uk</v>
+        <v>rtu@tyui.com</v>
       </c>
       <c r="C664" t="str">
-        <v>07365 367027</v>
+        <v>07440579926</v>
       </c>
       <c r="D664" t="str">
-        <v>REO Homes</v>
+        <v/>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Ross Newman</v>
+        <v>Rosemary Ni Sassi</v>
       </c>
       <c r="B665" t="str">
-        <v>info@rnewmanconstruction.co.uk</v>
+        <v>rns@Qapartments.com</v>
       </c>
       <c r="C665" t="str">
-        <v>+447804599880</v>
+        <v>+44 20 3404 4040</v>
       </c>
       <c r="D665" t="str">
         <v/>
@@ -30370,97 +30370,97 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Rowena</v>
+        <v>Rosie (REO Homes)</v>
       </c>
       <c r="B666" t="str">
-        <v>FAKE1@airbnb.com</v>
+        <v>info@reohomes.co.uk</v>
       </c>
       <c r="C666" t="str">
-        <v>0000220000</v>
+        <v>07365 367027</v>
       </c>
       <c r="D666" t="str">
-        <v>airbnbsd.com</v>
+        <v>REO Homes</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Rui</v>
+        <v>Ross Newman</v>
       </c>
       <c r="B667" t="str">
-        <v>velosopropertiesltd@gmail.com</v>
+        <v>info@rnewmanconstruction.co.uk</v>
       </c>
       <c r="C667" t="str">
-        <v>07913705797</v>
+        <v>+447804599880</v>
       </c>
       <c r="D667" t="str">
-        <v>velosoproperties</v>
+        <v/>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Russell Babylon Lane Lotties Luxury Lodge</v>
+        <v>Rowena</v>
       </c>
       <c r="B668" t="str">
-        <v>fake@lowerfarmestate.co.uk</v>
+        <v>FAKE1@airbnb.com</v>
       </c>
       <c r="C668" t="str">
-        <v>07887 504973</v>
+        <v>0000220000</v>
       </c>
       <c r="D668" t="str">
-        <v>lowerfarmestate.co.uk</v>
+        <v>airbnbsd.com</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Ryan Duffy</v>
+        <v>Rui</v>
       </c>
       <c r="B669" t="str">
-        <v>hello@ourhomeshortstays.co.uk</v>
+        <v>velosopropertiesltd@gmail.com</v>
       </c>
       <c r="C669" t="str">
-        <v>0330 190 0839</v>
+        <v>07913705797</v>
       </c>
       <c r="D669" t="str">
-        <v>Our Home Short Stays</v>
+        <v>velosoproperties</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Sabina</v>
+        <v>Russell Babylon Lane Lotties Luxury Lodge</v>
       </c>
       <c r="B670" t="str">
-        <v>agsmpropertymanagementltd@gmail.com</v>
+        <v>fake@lowerfarmestate.co.uk</v>
       </c>
       <c r="C670" t="str">
-        <v>+447417346461</v>
+        <v>07887 504973</v>
       </c>
       <c r="D670" t="str">
-        <v/>
+        <v>lowerfarmestate.co.uk</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Sabrina Allaway</v>
+        <v>Ryan Duffy</v>
       </c>
       <c r="B671" t="str">
-        <v>Sabrina@allayaypropinvest.com</v>
+        <v>hello@ourhomeshortstays.co.uk</v>
       </c>
       <c r="C671" t="str">
-        <v>+447709932330</v>
+        <v>0330 190 0839</v>
       </c>
       <c r="D671" t="str">
-        <v/>
+        <v>Our Home Short Stays</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Saheem</v>
+        <v>Sabina</v>
       </c>
       <c r="B672" t="str">
-        <v>info@dweller.com</v>
+        <v>agsmpropertymanagementltd@gmail.com</v>
       </c>
       <c r="C672" t="str">
-        <v>07708121409</v>
+        <v>+447417346461</v>
       </c>
       <c r="D672" t="str">
         <v/>
@@ -30468,13 +30468,13 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Salomon</v>
+        <v>Sabrina Allaway</v>
       </c>
       <c r="B673" t="str">
-        <v>temp3@airbnb.com</v>
+        <v>Sabrina@allayaypropinvest.com</v>
       </c>
       <c r="C673" t="str">
-        <v>07400775324</v>
+        <v>+447709932330</v>
       </c>
       <c r="D673" t="str">
         <v/>
@@ -30482,13 +30482,13 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Sam Hasni</v>
+        <v>Saheem</v>
       </c>
       <c r="B674" t="str">
-        <v>xxxxx@gmail.com</v>
+        <v>info@dweller.com</v>
       </c>
       <c r="C674" t="str">
-        <v>07487510083 / 07493065977</v>
+        <v>07708121409</v>
       </c>
       <c r="D674" t="str">
         <v/>
@@ -30496,13 +30496,13 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Sam Mourad</v>
+        <v>Salomon</v>
       </c>
       <c r="B675" t="str">
-        <v>blablabla@gmail.com</v>
+        <v>temp3@airbnb.com</v>
       </c>
       <c r="C675" t="str">
-        <v>07968527220</v>
+        <v>07400775324</v>
       </c>
       <c r="D675" t="str">
         <v/>
@@ -30510,83 +30510,83 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Sam Stabler</v>
+        <v>Sam Hasni</v>
       </c>
       <c r="B676" t="str">
-        <v>info@thetravelfox.co.uk</v>
+        <v>xxxxx@gmail.com</v>
       </c>
       <c r="C676" t="str">
-        <v>0808 175 0273</v>
+        <v>07487510083 / 07493065977</v>
       </c>
       <c r="D676" t="str">
-        <v>The Travel Fox</v>
+        <v/>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Samantha</v>
+        <v>Sam Mourad</v>
       </c>
       <c r="B677" t="str">
-        <v>sam@kozycottages.co.uk</v>
+        <v>blablabla@gmail.com</v>
       </c>
       <c r="C677" t="str">
-        <v xml:space="preserve"> +447747000597</v>
+        <v>07968527220</v>
       </c>
       <c r="D677" t="str">
-        <v>Kozy Cottages</v>
+        <v/>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Samantha</v>
+        <v>Sam Stabler</v>
       </c>
       <c r="B678" t="str">
-        <v>samantha303@hotmail.co.uk</v>
+        <v>info@thetravelfox.co.uk</v>
       </c>
       <c r="C678" t="str">
-        <v>07950 969345</v>
+        <v>0808 175 0273</v>
       </c>
       <c r="D678" t="str">
-        <v>Beddoe Apartments</v>
+        <v>The Travel Fox</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Samantha Kirkland</v>
+        <v>Samantha</v>
       </c>
       <c r="B679" t="str">
-        <v>bookings@azibistays.com</v>
+        <v>sam@kozycottages.co.uk</v>
       </c>
       <c r="C679" t="str">
-        <v>+447362224185</v>
+        <v xml:space="preserve"> +447747000597</v>
       </c>
       <c r="D679" t="str">
-        <v/>
+        <v>Kozy Cottages</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Samy Nada</v>
+        <v>Samantha</v>
       </c>
       <c r="B680" t="str">
-        <v>sami_nada@yahoo.com</v>
+        <v>samantha303@hotmail.co.uk</v>
       </c>
       <c r="C680" t="str">
-        <v>+44 7506 666620</v>
+        <v>07950 969345</v>
       </c>
       <c r="D680" t="str">
-        <v/>
+        <v>Beddoe Apartments</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Sandy</v>
+        <v>Samantha Kirkland</v>
       </c>
       <c r="B681" t="str">
-        <v>sandysherrington@live.co.uk</v>
+        <v>bookings@azibistays.com</v>
       </c>
       <c r="C681" t="str">
-        <v>07446 886489</v>
+        <v>+447362224185</v>
       </c>
       <c r="D681" t="str">
         <v/>
@@ -30594,13 +30594,13 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Sanjay | Airbnb</v>
+        <v>Samy Nada</v>
       </c>
       <c r="B682" t="str">
-        <v>sanjay@gmail.com</v>
+        <v>sami_nada@yahoo.com</v>
       </c>
       <c r="C682" t="str">
-        <v>112233445566</v>
+        <v>+44 7506 666620</v>
       </c>
       <c r="D682" t="str">
         <v/>
@@ -30608,69 +30608,69 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Saqib Choudbury</v>
+        <v>Sandy</v>
       </c>
       <c r="B683" t="str">
-        <v>info@suitepropertymanagement.co.uk</v>
+        <v>sandysherrington@live.co.uk</v>
       </c>
       <c r="C683" t="str">
-        <v>07852 761089</v>
+        <v>07446 886489</v>
       </c>
       <c r="D683" t="str">
-        <v>Suite Stays</v>
+        <v/>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Sara &amp; Shuayb</v>
+        <v>Sanjay | Airbnb</v>
       </c>
       <c r="B684" t="str">
-        <v>shuayb@urbangetaways.co.uk</v>
+        <v>sanjay@gmail.com</v>
       </c>
       <c r="C684" t="str">
-        <v>07756533485</v>
+        <v>112233445566</v>
       </c>
       <c r="D684" t="str">
-        <v>Urban Getaways Serviced Apartments</v>
+        <v/>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Sarah</v>
+        <v>Saqib Choudbury</v>
       </c>
       <c r="B685" t="str">
-        <v>dfgh@dfgh.com</v>
+        <v>info@suitepropertymanagement.co.uk</v>
       </c>
       <c r="C685" t="str">
-        <v>+447956 377272</v>
+        <v>07852 761089</v>
       </c>
       <c r="D685" t="str">
-        <v/>
+        <v>Suite Stays</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Sarah</v>
+        <v>Sara &amp; Shuayb</v>
       </c>
       <c r="B686" t="str">
-        <v>fakesarah@mail.com</v>
+        <v>shuayb@urbangetaways.co.uk</v>
       </c>
       <c r="C686" t="str">
-        <v>07791872947</v>
+        <v>07756533485</v>
       </c>
       <c r="D686" t="str">
-        <v/>
+        <v>Urban Getaways Serviced Apartments</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Sarah Bain Be My Guest</v>
+        <v>Sarah</v>
       </c>
       <c r="B687" t="str">
-        <v>bookings@bemyguestliverpool.co.uk</v>
+        <v>dfgh@dfgh.com</v>
       </c>
       <c r="C687" t="str">
-        <v>07730 772 279</v>
+        <v>+447956 377272</v>
       </c>
       <c r="D687" t="str">
         <v/>
@@ -30678,27 +30678,27 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Sarah Chelsea</v>
+        <v>Sarah</v>
       </c>
       <c r="B688" t="str">
-        <v>sarahchelsea@yahoo.com</v>
+        <v>fakesarah@mail.com</v>
       </c>
       <c r="C688" t="str">
-        <v>07951244998</v>
+        <v>07791872947</v>
       </c>
       <c r="D688" t="str">
-        <v>Airbnb</v>
+        <v/>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Sarah Fuell</v>
+        <v>Sarah Bain Be My Guest</v>
       </c>
       <c r="B689" t="str">
-        <v>sarahfuell@gmail.com</v>
+        <v>bookings@bemyguestliverpool.co.uk</v>
       </c>
       <c r="C689" t="str">
-        <v>+44 7979 064718</v>
+        <v>07730 772 279</v>
       </c>
       <c r="D689" t="str">
         <v/>
@@ -30706,181 +30706,181 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Sarah Mout</v>
+        <v>Sarah Chelsea</v>
       </c>
       <c r="B690" t="str">
-        <v>sarah@gmail.com</v>
+        <v>sarahchelsea@yahoo.com</v>
       </c>
       <c r="C690" t="str">
-        <v>07796167431</v>
+        <v>07951244998</v>
       </c>
       <c r="D690" t="str">
-        <v/>
+        <v>Airbnb</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Sarah Popoola</v>
+        <v>Sarah Fuell</v>
       </c>
       <c r="B691" t="str">
-        <v>hello@spjphomes.com</v>
+        <v>sarahfuell@gmail.com</v>
       </c>
       <c r="C691" t="str">
-        <v>07356068909</v>
+        <v>+44 7979 064718</v>
       </c>
       <c r="D691" t="str">
-        <v>SPJP Homes</v>
+        <v/>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Sasan</v>
+        <v>Sarah Mout</v>
       </c>
       <c r="B692" t="str">
-        <v>info@antiquerug.co.uk</v>
+        <v>sarah@gmail.com</v>
       </c>
       <c r="C692" t="str">
-        <v>+4423 80558054</v>
+        <v>07796167431</v>
       </c>
       <c r="D692" t="str">
-        <v>https://sasanian.co.uk/about.php</v>
+        <v/>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Sasha Herman</v>
+        <v>Sarah Popoola</v>
       </c>
       <c r="B693" t="str">
-        <v>yourstay@jesswoodproperties.com</v>
+        <v>hello@spjphomes.com</v>
       </c>
       <c r="C693" t="str">
-        <v>0203 603 8922</v>
+        <v>07356068909</v>
       </c>
       <c r="D693" t="str">
-        <v>Jesswood Properties</v>
+        <v>SPJP Homes</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Scott Blue</v>
+        <v>Sasan</v>
       </c>
       <c r="B694" t="str">
-        <v>hello@blueskiesstays.co.uk</v>
+        <v>info@antiquerug.co.uk</v>
       </c>
       <c r="C694" t="str">
-        <v>01642 205204</v>
+        <v>+4423 80558054</v>
       </c>
       <c r="D694" t="str">
-        <v>Blue Skies Stays</v>
+        <v>https://sasanian.co.uk/about.php</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Sean Elliott</v>
+        <v>Sasha Herman</v>
       </c>
       <c r="B695" t="str">
-        <v>bookings@stayswithfcd.com</v>
+        <v>yourstay@jesswoodproperties.com</v>
       </c>
       <c r="C695" t="str">
-        <v>+447715488582</v>
+        <v>0203 603 8922</v>
       </c>
       <c r="D695" t="str">
-        <v>Stays with FCD</v>
+        <v>Jesswood Properties</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Sean Grindlay</v>
+        <v>Scott Blue</v>
       </c>
       <c r="B696" t="str">
-        <v>info@staysavvyaccommodation.com</v>
+        <v>hello@blueskiesstays.co.uk</v>
       </c>
       <c r="C696" t="str">
-        <v>07712555076</v>
+        <v>01642 205204</v>
       </c>
       <c r="D696" t="str">
-        <v>StaySavvy Accommodation</v>
+        <v>Blue Skies Stays</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Selina - Maison Christo Property</v>
+        <v>Sean Elliott</v>
       </c>
       <c r="B697" t="str">
-        <v>info@maisonchristoproperty.com</v>
+        <v>bookings@stayswithfcd.com</v>
       </c>
       <c r="C697" t="str">
-        <v>07904842776</v>
+        <v>+447715488582</v>
       </c>
       <c r="D697" t="str">
-        <v>Maison Christo Property</v>
+        <v>Stays with FCD</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>Shams</v>
+        <v>Sean Grindlay</v>
       </c>
       <c r="B698" t="str">
-        <v>info@findyourdwelling.com</v>
+        <v>info@staysavvyaccommodation.com</v>
       </c>
       <c r="C698" t="str">
-        <v>020 8087 3161</v>
+        <v>07712555076</v>
       </c>
       <c r="D698" t="str">
-        <v>find your dwelling</v>
+        <v>StaySavvy Accommodation</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>Shan</v>
+        <v>Selina - Maison Christo Property</v>
       </c>
       <c r="B699" t="str">
-        <v>gcdjtgfn@cfgkytdj.com</v>
+        <v>info@maisonchristoproperty.com</v>
       </c>
       <c r="C699" t="str">
-        <v>07984978371</v>
+        <v>07904842776</v>
       </c>
       <c r="D699" t="str">
-        <v/>
+        <v>Maison Christo Property</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>Shan</v>
+        <v>Shams</v>
       </c>
       <c r="B700" t="str">
-        <v>sdfg@sdfg.com</v>
+        <v>info@findyourdwelling.com</v>
       </c>
       <c r="C700" t="str">
-        <v>+447984978371</v>
+        <v>020 8087 3161</v>
       </c>
       <c r="D700" t="str">
-        <v/>
+        <v>find your dwelling</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Shane</v>
+        <v>Shan</v>
       </c>
       <c r="B701" t="str">
-        <v>SERENITYSTAYSUK@OUTLOOK.COM</v>
+        <v>gcdjtgfn@cfgkytdj.com</v>
       </c>
       <c r="C701" t="str">
-        <v>07954491302</v>
+        <v>07984978371</v>
       </c>
       <c r="D701" t="str">
-        <v>Serenity Stays UK</v>
+        <v/>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Shanna</v>
+        <v>Shan</v>
       </c>
       <c r="B702" t="str">
-        <v>shanna@fake.com</v>
+        <v>sdfg@sdfg.com</v>
       </c>
       <c r="C702" t="str">
-        <v>7903635218</v>
+        <v>+447984978371</v>
       </c>
       <c r="D702" t="str">
         <v/>
@@ -30888,27 +30888,27 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Shanna</v>
+        <v>Shane</v>
       </c>
       <c r="B703" t="str">
-        <v>Buttonsestates@gmail.com</v>
+        <v>SERENITYSTAYSUK@OUTLOOK.COM</v>
       </c>
       <c r="C703" t="str">
-        <v>447903635218</v>
+        <v>07954491302</v>
       </c>
       <c r="D703" t="str">
-        <v/>
+        <v>Serenity Stays UK</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>Sharon Andjelkovic</v>
+        <v>Shanna</v>
       </c>
       <c r="B704" t="str">
-        <v>sharon.sigroup01@gmail.com</v>
+        <v>shanna@fake.com</v>
       </c>
       <c r="C704" t="str">
-        <v>+44 7308 887775</v>
+        <v>7903635218</v>
       </c>
       <c r="D704" t="str">
         <v/>
@@ -30916,13 +30916,13 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>Sharon Henwood</v>
+        <v>Shanna</v>
       </c>
       <c r="B705" t="str">
-        <v>henwoodhomestays@gmail.com</v>
+        <v>Buttonsestates@gmail.com</v>
       </c>
       <c r="C705" t="str">
-        <v>07795805651</v>
+        <v>447903635218</v>
       </c>
       <c r="D705" t="str">
         <v/>
@@ -30930,13 +30930,13 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>Sharon Lowestoft</v>
+        <v>Sharon Andjelkovic</v>
       </c>
       <c r="B706" t="str">
-        <v>dont123@airNOT.com</v>
+        <v>sharon.sigroup01@gmail.com</v>
       </c>
       <c r="C706" t="str">
-        <v>07306 590244</v>
+        <v>+44 7308 887775</v>
       </c>
       <c r="D706" t="str">
         <v/>
@@ -30944,13 +30944,13 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>Shaun Newbold</v>
+        <v>Sharon Henwood</v>
       </c>
       <c r="B707" t="str">
-        <v>shaun@flexi-lets.co.uk</v>
+        <v>henwoodhomestays@gmail.com</v>
       </c>
       <c r="C707" t="str">
-        <v>01252 210533</v>
+        <v>07795805651</v>
       </c>
       <c r="D707" t="str">
         <v/>
@@ -30958,13 +30958,13 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>Shaun, Ella wolstenholme</v>
+        <v>Sharon Lowestoft</v>
       </c>
       <c r="B708" t="str">
-        <v>faake@gmail.ocm</v>
+        <v>dont123@airNOT.com</v>
       </c>
       <c r="C708" t="str">
-        <v>07971835875</v>
+        <v>07306 590244</v>
       </c>
       <c r="D708" t="str">
         <v/>
@@ -30972,13 +30972,13 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>Shauna</v>
+        <v>Shaun Newbold</v>
       </c>
       <c r="B709" t="str">
-        <v>email@shauna.com</v>
+        <v>shaun@flexi-lets.co.uk</v>
       </c>
       <c r="C709" t="str">
-        <v>+44 7798 885843</v>
+        <v>01252 210533</v>
       </c>
       <c r="D709" t="str">
         <v/>
@@ -30986,27 +30986,27 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>Shay</v>
+        <v>Shaun, Ella wolstenholme</v>
       </c>
       <c r="B710" t="str">
-        <v>EDWINHARRISLDN@GMAIL.COM</v>
+        <v>faake@gmail.ocm</v>
       </c>
       <c r="C710" t="str">
-        <v>07425533111</v>
+        <v>07971835875</v>
       </c>
       <c r="D710" t="str">
-        <v>EDWIN HARRIS LTD</v>
+        <v/>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>Shay Griffin</v>
+        <v>Shauna</v>
       </c>
       <c r="B711" t="str">
-        <v>gbhgj@trhytju.com</v>
+        <v>email@shauna.com</v>
       </c>
       <c r="C711" t="str">
-        <v>074255333111</v>
+        <v>+44 7798 885843</v>
       </c>
       <c r="D711" t="str">
         <v/>
@@ -31014,27 +31014,27 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>Shehnaz Vorajee</v>
+        <v>Shay</v>
       </c>
       <c r="B712" t="str">
-        <v>shehnaz@vorajee.com</v>
+        <v>EDWINHARRISLDN@GMAIL.COM</v>
       </c>
       <c r="C712" t="str">
-        <v>+44 7583 093625</v>
+        <v>07425533111</v>
       </c>
       <c r="D712" t="str">
-        <v/>
+        <v>EDWIN HARRIS LTD</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>Sheikh</v>
+        <v>Shay Griffin</v>
       </c>
       <c r="B713" t="str">
-        <v>FAKE@airbnb.com</v>
+        <v>gbhgj@trhytju.com</v>
       </c>
       <c r="C713" t="str">
-        <v>00000000000</v>
+        <v>074255333111</v>
       </c>
       <c r="D713" t="str">
         <v/>
@@ -31042,13 +31042,13 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>Sheldon and Lesley</v>
+        <v>Shehnaz Vorajee</v>
       </c>
       <c r="B714" t="str">
-        <v>sheles@gmail.com</v>
+        <v>shehnaz@vorajee.com</v>
       </c>
       <c r="C714" t="str">
-        <v>07411 232199</v>
+        <v>+44 7583 093625</v>
       </c>
       <c r="D714" t="str">
         <v/>
@@ -31056,111 +31056,111 @@
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>Shelina Ratansi</v>
+        <v>Sheikh</v>
       </c>
       <c r="B715" t="str">
-        <v>info@srkaccommodation.co.uk</v>
+        <v>FAKE@airbnb.com</v>
       </c>
       <c r="C715" t="str">
-        <v>07771 550090</v>
+        <v>00000000000</v>
       </c>
       <c r="D715" t="str">
-        <v>SRK Accommodation</v>
+        <v/>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>Shiraz WHATSAPP only</v>
+        <v>Sheldon and Lesley</v>
       </c>
       <c r="B716" t="str">
-        <v>hello@caliberstays.co.uk</v>
+        <v>sheles@gmail.com</v>
       </c>
       <c r="C716" t="str">
-        <v>01216302101</v>
+        <v>07411 232199</v>
       </c>
       <c r="D716" t="str">
-        <v>Caliber Stays</v>
+        <v/>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>Shloime</v>
+        <v>Shelina Ratansi</v>
       </c>
       <c r="B717" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>info@srkaccommodation.co.uk</v>
       </c>
       <c r="C717" t="str">
-        <v>07867290839</v>
+        <v>07771 550090</v>
       </c>
       <c r="D717" t="str">
-        <v>Home to Host</v>
+        <v>SRK Accommodation</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>Shona Caulton</v>
+        <v>Shiraz WHATSAPP only</v>
       </c>
       <c r="B718" t="str">
-        <v>shona@falke.com</v>
+        <v>hello@caliberstays.co.uk</v>
       </c>
       <c r="C718" t="str">
-        <v>07948274032</v>
+        <v>01216302101</v>
       </c>
       <c r="D718" t="str">
-        <v>Heronridge Properties</v>
+        <v>Caliber Stays</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>ShortLet Express</v>
+        <v>Shloime</v>
       </c>
       <c r="B719" t="str">
-        <v>bookings@shortletexpress.com</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="C719" t="str">
-        <v>+447866973587</v>
+        <v>07867290839</v>
       </c>
       <c r="D719" t="str">
-        <v/>
+        <v>Home to Host</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>Sian and Martin</v>
+        <v>Shona Caulton</v>
       </c>
       <c r="B720" t="str">
-        <v>sian@fake.com</v>
+        <v>shona@falke.com</v>
       </c>
       <c r="C720" t="str">
-        <v>07771557000</v>
+        <v>07948274032</v>
       </c>
       <c r="D720" t="str">
-        <v/>
+        <v>Heronridge Properties</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>Sico</v>
+        <v>ShortLet Express</v>
       </c>
       <c r="B721" t="str">
-        <v>Fofisher@googlemail.com</v>
+        <v>bookings@shortletexpress.com</v>
       </c>
       <c r="C721" t="str">
-        <v>07956344466</v>
+        <v>+447866973587</v>
       </c>
       <c r="D721" t="str">
-        <v>sico</v>
+        <v/>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v xml:space="preserve">Sid </v>
+        <v>Sian and Martin</v>
       </c>
       <c r="B722" t="str">
-        <v>ibsyed@hotmail.com</v>
+        <v>sian@fake.com</v>
       </c>
       <c r="C722" t="str">
-        <v>07957 399999</v>
+        <v>07771557000</v>
       </c>
       <c r="D722" t="str">
         <v/>
@@ -31168,167 +31168,167 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>Sidemersey Living</v>
+        <v>Sico</v>
       </c>
       <c r="B723" t="str">
-        <v>info@365-living.co.uk</v>
+        <v>Fofisher@googlemail.com</v>
       </c>
       <c r="C723" t="str">
-        <v>+441514523200</v>
+        <v>07956344466</v>
       </c>
       <c r="D723" t="str">
-        <v/>
+        <v>sico</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>Silva</v>
+        <v xml:space="preserve">Sid </v>
       </c>
       <c r="B724" t="str">
-        <v>hi@booksilva.com</v>
+        <v>ibsyed@hotmail.com</v>
       </c>
       <c r="C724" t="str">
-        <v>+44 (1234) 519 790</v>
+        <v>07957 399999</v>
       </c>
       <c r="D724" t="str">
-        <v>https://booksilva.com/</v>
+        <v/>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>Silver sheds properties</v>
+        <v>Sidemersey Living</v>
       </c>
       <c r="B725" t="str">
-        <v>info@silvershedsproperties.com</v>
+        <v>info@365-living.co.uk</v>
       </c>
       <c r="C725" t="str">
-        <v xml:space="preserve"> 07446946204</v>
+        <v>+441514523200</v>
       </c>
       <c r="D725" t="str">
-        <v>Silver Sheds Properties</v>
+        <v/>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>Silverstag Properties</v>
+        <v>Silva</v>
       </c>
       <c r="B726" t="str">
-        <v>Bookings@silverstag-properties.co.uk</v>
+        <v>hi@booksilva.com</v>
       </c>
       <c r="C726" t="str">
-        <v xml:space="preserve"> +44 7432 423072</v>
+        <v>+44 (1234) 519 790</v>
       </c>
       <c r="D726" t="str">
-        <v/>
+        <v>https://booksilva.com/</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>Siman Kooner</v>
+        <v>Silver sheds properties</v>
       </c>
       <c r="B727" t="str">
-        <v>enquiries@reallushproperties.com</v>
+        <v>info@silvershedsproperties.com</v>
       </c>
       <c r="C727" t="str">
-        <v>01902288172</v>
+        <v xml:space="preserve"> 07446946204</v>
       </c>
       <c r="D727" t="str">
-        <v>Real Lush Properties</v>
+        <v>Silver Sheds Properties</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>Simon</v>
+        <v>Silverstag Properties</v>
       </c>
       <c r="B728" t="str">
-        <v>stay@cotswoldaparthotel.co.uk</v>
+        <v>Bookings@silverstag-properties.co.uk</v>
       </c>
       <c r="C728" t="str">
-        <v>01453 764 496</v>
+        <v xml:space="preserve"> +44 7432 423072</v>
       </c>
       <c r="D728" t="str">
-        <v>Cotswold Apartment</v>
+        <v/>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v xml:space="preserve">Simon </v>
+        <v>Siman Kooner</v>
       </c>
       <c r="B729" t="str">
-        <v>reservations@bromleyservicedapartments.co.uk</v>
+        <v>enquiries@reallushproperties.com</v>
       </c>
       <c r="C729" t="str">
-        <v>07985197495</v>
+        <v>01902288172</v>
       </c>
       <c r="D729" t="str">
-        <v>Bromley Serviced Apartments</v>
+        <v>Real Lush Properties</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>Simon Hartco</v>
+        <v>Simon</v>
       </c>
       <c r="B730" t="str">
-        <v>hartcoservicedapartments@gmail.com</v>
+        <v>stay@cotswoldaparthotel.co.uk</v>
       </c>
       <c r="C730" t="str">
-        <v>0795962706</v>
+        <v>01453 764 496</v>
       </c>
       <c r="D730" t="str">
-        <v>Hartco serviced apartments</v>
+        <v>Cotswold Apartment</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v xml:space="preserve">Siobhan </v>
+        <v xml:space="preserve">Simon </v>
       </c>
       <c r="B731" t="str">
-        <v>hello@seafieldmanagement.com</v>
+        <v>reservations@bromleyservicedapartments.co.uk</v>
       </c>
       <c r="C731" t="str">
-        <v>+447730337056</v>
+        <v>07985197495</v>
       </c>
       <c r="D731" t="str">
-        <v>Seafield SA Management Ltd</v>
+        <v>Bromley Serviced Apartments</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>Sirina Muntaka</v>
+        <v>Simon Hartco</v>
       </c>
       <c r="B732" t="str">
-        <v>info@hananahomes.co.uk</v>
+        <v>hartcoservicedapartments@gmail.com</v>
       </c>
       <c r="C732" t="str">
-        <v>07482590277</v>
+        <v>0795962706</v>
       </c>
       <c r="D732" t="str">
-        <v/>
+        <v>Hartco serviced apartments</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>Smarthost</v>
+        <v xml:space="preserve">Siobhan </v>
       </c>
       <c r="B733" t="str">
-        <v>london@smarthost.co.uk</v>
+        <v>hello@seafieldmanagement.com</v>
       </c>
       <c r="C733" t="str">
-        <v>+44 2078702393</v>
+        <v>+447730337056</v>
       </c>
       <c r="D733" t="str">
-        <v/>
+        <v>Seafield SA Management Ltd</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>Sofia(Don't Contact)</v>
+        <v>Sirina Muntaka</v>
       </c>
       <c r="B734" t="str">
-        <v>sofia.decrescentiis@gmail.com</v>
+        <v>info@hananahomes.co.uk</v>
       </c>
       <c r="C734" t="str">
-        <v>07715419122</v>
+        <v>07482590277</v>
       </c>
       <c r="D734" t="str">
         <v/>
@@ -31336,13 +31336,13 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>Solari Living</v>
+        <v>Smarthost</v>
       </c>
       <c r="B735" t="str">
-        <v>Jontai@solariliving.co.uk</v>
+        <v>london@smarthost.co.uk</v>
       </c>
       <c r="C735" t="str">
-        <v>+447957918446</v>
+        <v>+44 2078702393</v>
       </c>
       <c r="D735" t="str">
         <v/>
@@ -31350,27 +31350,27 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>Solid Rock Estates</v>
+        <v>Sofia(Don't Contact)</v>
       </c>
       <c r="B736" t="str">
-        <v>admin@SolidRockEstates.com</v>
+        <v>sofia.decrescentiis@gmail.com</v>
       </c>
       <c r="C736" t="str">
-        <v>07739 474478</v>
+        <v>07715419122</v>
       </c>
       <c r="D736" t="str">
-        <v>UK London Apartment / SolidRock Eststes</v>
+        <v/>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>Solomon</v>
+        <v>Solari Living</v>
       </c>
       <c r="B737" t="str">
-        <v>arimbsproperties@gmail.com</v>
+        <v>Jontai@solariliving.co.uk</v>
       </c>
       <c r="C737" t="str">
-        <v>+44 7400 775324</v>
+        <v>+447957918446</v>
       </c>
       <c r="D737" t="str">
         <v/>
@@ -31378,27 +31378,27 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>Solomon and Jacquline</v>
+        <v>Solid Rock Estates</v>
       </c>
       <c r="B738" t="str">
-        <v>fake1@email.com</v>
+        <v>admin@SolidRockEstates.com</v>
       </c>
       <c r="C738" t="str">
-        <v>07400775324</v>
+        <v>07739 474478</v>
       </c>
       <c r="D738" t="str">
-        <v/>
+        <v>UK London Apartment / SolidRock Eststes</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>Sophia Dick</v>
+        <v>Solomon</v>
       </c>
       <c r="B739" t="str">
-        <v>info@iturastay.com</v>
+        <v>arimbsproperties@gmail.com</v>
       </c>
       <c r="C739" t="str">
-        <v xml:space="preserve"> 0203 576 5615</v>
+        <v>+44 7400 775324</v>
       </c>
       <c r="D739" t="str">
         <v/>
@@ -31406,13 +31406,13 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>Sophie</v>
+        <v>Solomon and Jacquline</v>
       </c>
       <c r="B740" t="str">
-        <v>soph@gmail.com</v>
+        <v>fake1@email.com</v>
       </c>
       <c r="C740" t="str">
-        <v>+44 7723853912</v>
+        <v>07400775324</v>
       </c>
       <c r="D740" t="str">
         <v/>
@@ -31420,13 +31420,13 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>Sophie BS7</v>
+        <v>Sophia Dick</v>
       </c>
       <c r="B741" t="str">
-        <v>fake20@fake.com</v>
+        <v>info@iturastay.com</v>
       </c>
       <c r="C741" t="str">
-        <v>07305257946</v>
+        <v xml:space="preserve"> 0203 576 5615</v>
       </c>
       <c r="D741" t="str">
         <v/>
@@ -31434,13 +31434,13 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>Sorcha</v>
+        <v>Sophie</v>
       </c>
       <c r="B742" t="str">
-        <v>sorcha@fakeemail.com</v>
+        <v>soph@gmail.com</v>
       </c>
       <c r="C742" t="str">
-        <v>07817802878</v>
+        <v>+44 7723853912</v>
       </c>
       <c r="D742" t="str">
         <v/>
@@ -31448,27 +31448,27 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>Spencer</v>
+        <v>Sophie BS7</v>
       </c>
       <c r="B743" t="str">
-        <v>bootsurveying@gmail.com</v>
+        <v>fake20@fake.com</v>
       </c>
       <c r="C743" t="str">
-        <v>+447368235513</v>
+        <v>07305257946</v>
       </c>
       <c r="D743" t="str">
-        <v>Royal Boot Stays</v>
+        <v/>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>Stai</v>
+        <v>Sorcha</v>
       </c>
       <c r="B744" t="str">
-        <v>info@stai.co.uk</v>
+        <v>sorcha@fakeemail.com</v>
       </c>
       <c r="C744" t="str">
-        <v>07510 373969</v>
+        <v>07817802878</v>
       </c>
       <c r="D744" t="str">
         <v/>
@@ -31476,125 +31476,125 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>Stan Stoynav</v>
+        <v>Spencer</v>
       </c>
       <c r="B745" t="str">
-        <v>StanStoynav@svsbuilderslttd.com</v>
+        <v>bootsurveying@gmail.com</v>
       </c>
       <c r="C745" t="str">
-        <v>+44 7908 957363</v>
+        <v>+447368235513</v>
       </c>
       <c r="D745" t="str">
-        <v>SVS Invest Ltd</v>
+        <v>Royal Boot Stays</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>Stanley</v>
+        <v>Stai</v>
       </c>
       <c r="B746" t="str">
-        <v>inof@opulent-homes.co.uk</v>
+        <v>info@stai.co.uk</v>
       </c>
       <c r="C746" t="str">
-        <v>0203 633 2961</v>
+        <v>07510 373969</v>
       </c>
       <c r="D746" t="str">
-        <v>Opulent Homes</v>
+        <v/>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>Starhost Residences</v>
+        <v>Stan Stoynav</v>
       </c>
       <c r="B747" t="str">
-        <v>enquiries@starhost-residences.uk</v>
+        <v>StanStoynav@svsbuilderslttd.com</v>
       </c>
       <c r="C747" t="str">
-        <v xml:space="preserve"> +44 (0)333 900 1300</v>
+        <v>+44 7908 957363</v>
       </c>
       <c r="D747" t="str">
-        <v>StarHost Residences</v>
+        <v>SVS Invest Ltd</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>Stay Hotel Huddersfield</v>
+        <v>Stanley</v>
       </c>
       <c r="B748" t="str">
-        <v>gm@stayhotel.co.uk</v>
+        <v>inof@opulent-homes.co.uk</v>
       </c>
       <c r="C748" t="str">
-        <v>01484 955559</v>
+        <v>0203 633 2961</v>
       </c>
       <c r="D748" t="str">
-        <v/>
+        <v>Opulent Homes</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>StayCasa</v>
+        <v>Starhost Residences</v>
       </c>
       <c r="B749" t="str">
-        <v>hello@staycasa.co.uk</v>
+        <v>enquiries@starhost-residences.uk</v>
       </c>
       <c r="C749" t="str">
-        <v>07933 034418</v>
+        <v xml:space="preserve"> +44 (0)333 900 1300</v>
       </c>
       <c r="D749" t="str">
-        <v>StayCasa</v>
+        <v>StarHost Residences</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>Staybridge Suites Birmingham</v>
+        <v>Stay Hotel Huddersfield</v>
       </c>
       <c r="B750" t="str">
-        <v>gsa@birmingham.staybridge.com</v>
+        <v>gm@stayhotel.co.uk</v>
       </c>
       <c r="C750" t="str">
-        <v>01212893636</v>
+        <v>01484 955559</v>
       </c>
       <c r="D750" t="str">
-        <v>https://staybridgesuites.hotels-birmingham.net/en/</v>
+        <v/>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>Stedroy Duberry</v>
+        <v>StayCasa</v>
       </c>
       <c r="B751" t="str">
-        <v>scabey@gmail.com</v>
+        <v>hello@staycasa.co.uk</v>
       </c>
       <c r="C751" t="str">
-        <v>+44 7868 162384</v>
+        <v>07933 034418</v>
       </c>
       <c r="D751" t="str">
-        <v/>
+        <v>StayCasa</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>Steve Garner</v>
+        <v>Staybridge Suites Birmingham</v>
       </c>
       <c r="B752" t="str">
-        <v>steve@glendowerbb.com</v>
+        <v>gsa@birmingham.staybridge.com</v>
       </c>
       <c r="C752" t="str">
-        <v xml:space="preserve">01362 652 960 </v>
+        <v>01212893636</v>
       </c>
       <c r="D752" t="str">
-        <v>Glendower Apartments</v>
+        <v>https://staybridgesuites.hotels-birmingham.net/en/</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>Steve Mallet</v>
+        <v>Stedroy Duberry</v>
       </c>
       <c r="B753" t="str">
-        <v>steve@themallets.co.uk</v>
+        <v>scabey@gmail.com</v>
       </c>
       <c r="C753" t="str">
-        <v>+447770274528</v>
+        <v>+44 7868 162384</v>
       </c>
       <c r="D753" t="str">
         <v/>
@@ -31602,97 +31602,97 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v xml:space="preserve">Steven </v>
+        <v>Steve Garner</v>
       </c>
       <c r="B754" t="str">
-        <v>steve@manhattanpropertysolutions.co.uk</v>
+        <v>steve@glendowerbb.com</v>
       </c>
       <c r="C754" t="str">
-        <v>07454753267</v>
+        <v xml:space="preserve">01362 652 960 </v>
       </c>
       <c r="D754" t="str">
-        <v>Blackberry cottage</v>
+        <v>Glendower Apartments</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>Steven Rich</v>
+        <v>Steve Mallet</v>
       </c>
       <c r="B755" t="str">
-        <v>steven@stevenrichproperty.co.uk</v>
+        <v>steve@themallets.co.uk</v>
       </c>
       <c r="C755" t="str">
-        <v>+447532108717</v>
+        <v>+447770274528</v>
       </c>
       <c r="D755" t="str">
-        <v>RPI Stays 1 Ltd</v>
+        <v/>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>Steven Veeramootoo</v>
+        <v xml:space="preserve">Steven </v>
       </c>
       <c r="B756" t="str">
-        <v>stevenv2701@gmail.com</v>
+        <v>steve@manhattanpropertysolutions.co.uk</v>
       </c>
       <c r="C756" t="str">
-        <v>07737913489</v>
+        <v>07454753267</v>
       </c>
       <c r="D756" t="str">
-        <v>Homelystaysuk</v>
+        <v>Blackberry cottage</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>Stress Free Homes</v>
+        <v>Steven Rich</v>
       </c>
       <c r="B757" t="str">
-        <v>enquiries@yourstressfreeproperties.com</v>
+        <v>steven@stevenrichproperty.co.uk</v>
       </c>
       <c r="C757" t="str">
-        <v>020 3488 9972</v>
+        <v>+447532108717</v>
       </c>
       <c r="D757" t="str">
-        <v>https://yourstressfreeproperties.com/</v>
+        <v>RPI Stays 1 Ltd</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>Stuart</v>
+        <v>Steven Veeramootoo</v>
       </c>
       <c r="B758" t="str">
-        <v>Noemail@fake.com</v>
+        <v>stevenv2701@gmail.com</v>
       </c>
       <c r="C758" t="str">
-        <v>07900887720</v>
+        <v>07737913489</v>
       </c>
       <c r="D758" t="str">
-        <v/>
+        <v>Homelystaysuk</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>Suhanur</v>
+        <v>Stress Free Homes</v>
       </c>
       <c r="B759" t="str">
-        <v>fake@thejoystay.com</v>
+        <v>enquiries@yourstressfreeproperties.com</v>
       </c>
       <c r="C759" t="str">
-        <v>07932767619</v>
+        <v>020 3488 9972</v>
       </c>
       <c r="D759" t="str">
-        <v>The Joy Stay</v>
+        <v>https://yourstressfreeproperties.com/</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>Sultan Khan</v>
+        <v>Stuart</v>
       </c>
       <c r="B760" t="str">
-        <v>Noemailemail@email.com</v>
+        <v>Noemail@fake.com</v>
       </c>
       <c r="C760" t="str">
-        <v>07769755700</v>
+        <v>07900887720</v>
       </c>
       <c r="D760" t="str">
         <v/>
@@ -31700,27 +31700,27 @@
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>Surya Gupta</v>
+        <v>Suhanur</v>
       </c>
       <c r="B761" t="str">
-        <v>info@brumstay.com</v>
+        <v>fake@thejoystay.com</v>
       </c>
       <c r="C761" t="str">
-        <v>+44 7826 312678</v>
+        <v>07932767619</v>
       </c>
       <c r="D761" t="str">
-        <v>Brum Stays UK</v>
+        <v>The Joy Stay</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>Susan &amp; Simon</v>
+        <v>Sultan Khan</v>
       </c>
       <c r="B762" t="str">
-        <v>noemail@gmail.com</v>
+        <v>Noemailemail@email.com</v>
       </c>
       <c r="C762" t="str">
-        <v>07533267580</v>
+        <v>07769755700</v>
       </c>
       <c r="D762" t="str">
         <v/>
@@ -31728,125 +31728,125 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>Susan Crockett</v>
+        <v>Surya Gupta</v>
       </c>
       <c r="B763" t="str">
-        <v>suzannwc64@hotmail.com</v>
+        <v>info@brumstay.com</v>
       </c>
       <c r="C763" t="str">
-        <v>07824 865112</v>
+        <v>+44 7826 312678</v>
       </c>
       <c r="D763" t="str">
-        <v/>
+        <v>Brum Stays UK</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>Susan Duncan</v>
+        <v>Susan &amp; Simon</v>
       </c>
       <c r="B764" t="str">
-        <v>info@hayloftedinburgh.com</v>
+        <v>noemail@gmail.com</v>
       </c>
       <c r="C764" t="str">
-        <v>07747127779</v>
+        <v>07533267580</v>
       </c>
       <c r="D764" t="str">
-        <v>hayloftedinburgh.com</v>
+        <v/>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>Suzy Sandhu</v>
+        <v>Susan Crockett</v>
       </c>
       <c r="B765" t="str">
-        <v>suzy@bnbguru.co.uk</v>
+        <v>suzannwc64@hotmail.com</v>
       </c>
       <c r="C765" t="str">
-        <v>441417397700</v>
+        <v>07824 865112</v>
       </c>
       <c r="D765" t="str">
-        <v>BNB Guru</v>
+        <v/>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>Swift-Host Team</v>
+        <v>Susan Duncan</v>
       </c>
       <c r="B766" t="str">
-        <v>stay@swift-host.co.uk</v>
+        <v>info@hayloftedinburgh.com</v>
       </c>
       <c r="C766" t="str">
-        <v>000000000</v>
+        <v>07747127779</v>
       </c>
       <c r="D766" t="str">
-        <v/>
+        <v>hayloftedinburgh.com</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>Syed</v>
+        <v>Suzy Sandhu</v>
       </c>
       <c r="B767" t="str">
-        <v>info@quartzluxuryproperties.com</v>
+        <v>suzy@bnbguru.co.uk</v>
       </c>
       <c r="C767" t="str">
-        <v>+44207-175-7368</v>
+        <v>441417397700</v>
       </c>
       <c r="D767" t="str">
-        <v>quartzluxuryproperties.com</v>
+        <v>BNB Guru</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>Sykes Cottages</v>
+        <v>Swift-Host Team</v>
       </c>
       <c r="B768" t="str">
-        <v>info@sykescottages.co.uk</v>
+        <v>stay@swift-host.co.uk</v>
       </c>
       <c r="C768" t="str">
-        <v>01244356695</v>
+        <v>000000000</v>
       </c>
       <c r="D768" t="str">
-        <v>Sykes Cottages</v>
+        <v/>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>TLC Stays</v>
+        <v>Syed</v>
       </c>
       <c r="B769" t="str">
-        <v>hello@tlcstay.co.uk</v>
+        <v>info@quartzluxuryproperties.com</v>
       </c>
       <c r="C769" t="str">
-        <v>+447476037735</v>
+        <v>+44207-175-7368</v>
       </c>
       <c r="D769" t="str">
-        <v/>
+        <v>quartzluxuryproperties.com</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>Tai</v>
+        <v>Sykes Cottages</v>
       </c>
       <c r="B770" t="str">
-        <v>guests@tlm-propertymanagement.com</v>
+        <v>info@sykescottages.co.uk</v>
       </c>
       <c r="C770" t="str">
-        <v>07717468233</v>
+        <v>01244356695</v>
       </c>
       <c r="D770" t="str">
-        <v/>
+        <v>Sykes Cottages</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>Tailored Properties</v>
+        <v>TLC Stays</v>
       </c>
       <c r="B771" t="str">
-        <v>contact@tailored-properties.co.uk</v>
+        <v>hello@tlcstay.co.uk</v>
       </c>
       <c r="C771" t="str">
-        <v>07927560784</v>
+        <v>+447476037735</v>
       </c>
       <c r="D771" t="str">
         <v/>
@@ -31854,139 +31854,139 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>Talha</v>
+        <v>Tai</v>
       </c>
       <c r="B772" t="str">
-        <v>cozynightsinnltd@gmail.com</v>
+        <v>guests@tlm-propertymanagement.com</v>
       </c>
       <c r="C772" t="str">
-        <v>07843850849</v>
+        <v>07717468233</v>
       </c>
       <c r="D772" t="str">
-        <v>Cozy Nights Inn</v>
+        <v/>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>Tanya Stankovic</v>
+        <v>Tailored Properties</v>
       </c>
       <c r="B773" t="str">
-        <v>thereyagroup@gmail.com</v>
+        <v>contact@tailored-properties.co.uk</v>
       </c>
       <c r="C773" t="str">
-        <v>+44 (0)7950297113</v>
+        <v>07927560784</v>
       </c>
       <c r="D773" t="str">
-        <v>Reya Group</v>
+        <v/>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>Tashan</v>
+        <v>Talha</v>
       </c>
       <c r="B774" t="str">
-        <v>contact.dreamresidence@gmail.com</v>
+        <v>cozynightsinnltd@gmail.com</v>
       </c>
       <c r="C774" t="str">
-        <v>07960373426</v>
+        <v>07843850849</v>
       </c>
       <c r="D774" t="str">
-        <v/>
+        <v>Cozy Nights Inn</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>Teddington Lodge</v>
+        <v>Tanya Stankovic</v>
       </c>
       <c r="B775" t="str">
-        <v>info@teddingtonlodge.com</v>
+        <v>thereyagroup@gmail.com</v>
       </c>
       <c r="C775" t="str">
-        <v>+44 (0)7307668888</v>
+        <v>+44 (0)7950297113</v>
       </c>
       <c r="D775" t="str">
-        <v/>
+        <v>Reya Group</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>Tellington Nyamurera</v>
+        <v>Tashan</v>
       </c>
       <c r="B776" t="str">
-        <v>Info@telly-homes.com</v>
+        <v>contact.dreamresidence@gmail.com</v>
       </c>
       <c r="C776" t="str">
-        <v>07949 978277</v>
+        <v>07960373426</v>
       </c>
       <c r="D776" t="str">
-        <v>Telly Homes</v>
+        <v/>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>Teresa</v>
+        <v>Teddington Lodge</v>
       </c>
       <c r="B777" t="str">
-        <v>info@kozyguru.com</v>
+        <v>info@teddingtonlodge.com</v>
       </c>
       <c r="C777" t="str">
-        <v>07873 407490</v>
+        <v>+44 (0)7307668888</v>
       </c>
       <c r="D777" t="str">
-        <v>Kozy Guru</v>
+        <v/>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>Tessa Thompson</v>
+        <v>Tellington Nyamurera</v>
       </c>
       <c r="B778" t="str">
-        <v>info@yourstaysolutions.co.uk</v>
+        <v>Info@telly-homes.com</v>
       </c>
       <c r="C778" t="str">
-        <v>07725503937</v>
+        <v>07949 978277</v>
       </c>
       <c r="D778" t="str">
-        <v>Your Stay Solutions</v>
+        <v>Telly Homes</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>Test</v>
+        <v>Teresa</v>
       </c>
       <c r="B779" t="str">
-        <v>alexandru.oprescu@outlook.com</v>
+        <v>info@kozyguru.com</v>
       </c>
       <c r="C779" t="str">
-        <v>0746163153</v>
+        <v>07873 407490</v>
       </c>
       <c r="D779" t="str">
-        <v/>
+        <v>Kozy Guru</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>Test</v>
+        <v>Tessa Thompson</v>
       </c>
       <c r="B780" t="str">
-        <v>alexandru.oprescu@yahoo.com</v>
+        <v>info@yourstaysolutions.co.uk</v>
       </c>
       <c r="C780" t="str">
-        <v>0746163153</v>
+        <v>07725503937</v>
       </c>
       <c r="D780" t="str">
-        <v/>
+        <v>Your Stay Solutions</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>Testing profile</v>
+        <v>Test</v>
       </c>
       <c r="B781" t="str">
-        <v>test@test.com</v>
+        <v>alexandru.oprescu@outlook.com</v>
       </c>
       <c r="C781" t="str">
-        <v>07462183441</v>
+        <v>0746163153</v>
       </c>
       <c r="D781" t="str">
         <v/>
@@ -31994,13 +31994,13 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>Tetteh Johnson</v>
+        <v>Test</v>
       </c>
       <c r="B782" t="str">
-        <v>info@tjohnrealestate.com</v>
+        <v>alexandru.oprescu@yahoo.com</v>
       </c>
       <c r="C782" t="str">
-        <v>+44 7938 164087</v>
+        <v>0746163153</v>
       </c>
       <c r="D782" t="str">
         <v/>
@@ -32008,27 +32008,27 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>Tham</v>
+        <v>Testing profile</v>
       </c>
       <c r="B783" t="str">
-        <v>airbn@gmail.com</v>
+        <v>test@test.com</v>
       </c>
       <c r="C783" t="str">
-        <v>07737178109</v>
+        <v>07462183441</v>
       </c>
       <c r="D783" t="str">
-        <v>airbnb</v>
+        <v/>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>Thandiwe</v>
+        <v>Tetteh Johnson</v>
       </c>
       <c r="B784" t="str">
-        <v>shortstaysolutions1@gmail.com</v>
+        <v>info@tjohnrealestate.com</v>
       </c>
       <c r="C784" t="str">
-        <v>+44741 2514 966</v>
+        <v>+44 7938 164087</v>
       </c>
       <c r="D784" t="str">
         <v/>
@@ -32036,27 +32036,27 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v xml:space="preserve">The Butler Collection </v>
+        <v>Tham</v>
       </c>
       <c r="B785" t="str">
-        <v>contact.us@butler-collection.com</v>
+        <v>airbn@gmail.com</v>
       </c>
       <c r="C785" t="str">
-        <v>01273 640281</v>
+        <v>07737178109</v>
       </c>
       <c r="D785" t="str">
-        <v/>
+        <v>airbnb</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>The Flex</v>
+        <v>Thandiwe</v>
       </c>
       <c r="B786" t="str">
-        <v>info@theflex.global</v>
+        <v>shortstaysolutions1@gmail.com</v>
       </c>
       <c r="C786" t="str">
-        <v>07723 745646</v>
+        <v>+44741 2514 966</v>
       </c>
       <c r="D786" t="str">
         <v/>
@@ -32064,13 +32064,13 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>The Gem House</v>
+        <v xml:space="preserve">The Butler Collection </v>
       </c>
       <c r="B787" t="str">
-        <v>info@thegemhouse.co.uk</v>
+        <v>contact.us@butler-collection.com</v>
       </c>
       <c r="C787" t="str">
-        <v>07460769448</v>
+        <v>01273 640281</v>
       </c>
       <c r="D787" t="str">
         <v/>
@@ -32078,27 +32078,27 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v xml:space="preserve">The Yorkshire Hosts </v>
+        <v>The Flex</v>
       </c>
       <c r="B788" t="str">
-        <v>hello@theyorkshirehosts.co.uk</v>
+        <v>info@theflex.global</v>
       </c>
       <c r="C788" t="str">
-        <v xml:space="preserve"> 07764524142</v>
+        <v>07723 745646</v>
       </c>
       <c r="D788" t="str">
-        <v>theyorkshirehosts.co.uk</v>
+        <v/>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>The is Vertus</v>
+        <v>The Gem House</v>
       </c>
       <c r="B789" t="str">
-        <v>reservations@vertusedit.com</v>
+        <v>info@thegemhouse.co.uk</v>
       </c>
       <c r="C789" t="str">
-        <v>02074182811</v>
+        <v>07460769448</v>
       </c>
       <c r="D789" t="str">
         <v/>
@@ -32106,27 +32106,27 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>Thomas Barrow</v>
+        <v xml:space="preserve">The Yorkshire Hosts </v>
       </c>
       <c r="B790" t="str">
-        <v>enquires@jonesrentalproperties.co.uk</v>
+        <v>hello@theyorkshirehosts.co.uk</v>
       </c>
       <c r="C790" t="str">
-        <v>07894686678</v>
+        <v xml:space="preserve"> 07764524142</v>
       </c>
       <c r="D790" t="str">
-        <v>Jones Rental Properties</v>
+        <v>theyorkshirehosts.co.uk</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>Tiffany Banes</v>
+        <v>The is Vertus</v>
       </c>
       <c r="B791" t="str">
-        <v>pa@townandspaces.com</v>
+        <v>reservations@vertusedit.com</v>
       </c>
       <c r="C791" t="str">
-        <v>02071014942</v>
+        <v>02074182811</v>
       </c>
       <c r="D791" t="str">
         <v/>
@@ -32134,83 +32134,83 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>Tifony</v>
+        <v>Thomas Barrow</v>
       </c>
       <c r="B792" t="str">
-        <v>fake@tifony.co.uk</v>
+        <v>enquires@jonesrentalproperties.co.uk</v>
       </c>
       <c r="C792" t="str">
-        <v xml:space="preserve"> +44 7899 650203</v>
+        <v>07894686678</v>
       </c>
       <c r="D792" t="str">
-        <v/>
+        <v>Jones Rental Properties</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>Tim &amp; Joanne Brown</v>
+        <v>Tiffany Banes</v>
       </c>
       <c r="B793" t="str">
-        <v>tim@jkconstruction.co.uk</v>
+        <v>pa@townandspaces.com</v>
       </c>
       <c r="C793" t="str">
-        <v>07752531720</v>
+        <v>02071014942</v>
       </c>
       <c r="D793" t="str">
-        <v>Tim &amp; Jo Brown</v>
+        <v/>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>Tina Cleary</v>
+        <v>Tifony</v>
       </c>
       <c r="B794" t="str">
-        <v>info@ultimatepropertyinvestments.co.uk</v>
+        <v>fake@tifony.co.uk</v>
       </c>
       <c r="C794" t="str">
-        <v>07966 031343</v>
+        <v xml:space="preserve"> +44 7899 650203</v>
       </c>
       <c r="D794" t="str">
-        <v>Ultimate Homes Away</v>
+        <v/>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>Tito | AVO apartments</v>
+        <v>Tim &amp; Joanne Brown</v>
       </c>
       <c r="B795" t="str">
-        <v>fakeemail@gmail.com</v>
+        <v>tim@jkconstruction.co.uk</v>
       </c>
       <c r="C795" t="str">
-        <v>07393341794</v>
+        <v>07752531720</v>
       </c>
       <c r="D795" t="str">
-        <v/>
+        <v>Tim &amp; Jo Brown</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>Tom (WF17)</v>
+        <v>Tina Cleary</v>
       </c>
       <c r="B796" t="str">
-        <v>TOMWF@gmail.com</v>
+        <v>info@ultimatepropertyinvestments.co.uk</v>
       </c>
       <c r="C796" t="str">
-        <v>01924 474456</v>
+        <v>07966 031343</v>
       </c>
       <c r="D796" t="str">
-        <v/>
+        <v>Ultimate Homes Away</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>Tom Chipchase</v>
+        <v>Tito | AVO apartments</v>
       </c>
       <c r="B797" t="str">
-        <v>temp1@airbnb.com</v>
+        <v>fakeemail@gmail.com</v>
       </c>
       <c r="C797" t="str">
-        <v>07500381235</v>
+        <v>07393341794</v>
       </c>
       <c r="D797" t="str">
         <v/>
@@ -32218,69 +32218,69 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>Tom Festa</v>
+        <v>Tom (WF17)</v>
       </c>
       <c r="B798" t="str">
-        <v>thomas@skyvista-servicedaccommodations.co.uk</v>
+        <v>TOMWF@gmail.com</v>
       </c>
       <c r="C798" t="str">
-        <v>07758621199</v>
+        <v>01924 474456</v>
       </c>
       <c r="D798" t="str">
-        <v>Airbnb</v>
+        <v/>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>Tom Hutchinson</v>
+        <v>Tom Chipchase</v>
       </c>
       <c r="B799" t="str">
-        <v>tom@else-where.co.uk</v>
+        <v>temp1@airbnb.com</v>
       </c>
       <c r="C799" t="str">
-        <v>02033 624 111</v>
+        <v>07500381235</v>
       </c>
       <c r="D799" t="str">
-        <v>Temp Stays</v>
+        <v/>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>Tom Lawrence</v>
+        <v>Tom Festa</v>
       </c>
       <c r="B800" t="str">
-        <v>info@tpl.properties</v>
+        <v>thomas@skyvista-servicedaccommodations.co.uk</v>
       </c>
       <c r="C800" t="str">
-        <v>07388570642</v>
+        <v>07758621199</v>
       </c>
       <c r="D800" t="str">
-        <v/>
+        <v>Airbnb</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v xml:space="preserve">Tom Stayzo </v>
+        <v>Tom Hutchinson</v>
       </c>
       <c r="B801" t="str">
-        <v>direct@stayzo.co.uk</v>
+        <v>tom@else-where.co.uk</v>
       </c>
       <c r="C801" t="str">
-        <v>01494629629</v>
+        <v>02033 624 111</v>
       </c>
       <c r="D801" t="str">
-        <v>07740472525</v>
+        <v>Temp Stays</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v xml:space="preserve">Tony / Danny </v>
+        <v>Tom Lawrence</v>
       </c>
       <c r="B802" t="str">
-        <v>dfghj@rtyu.com</v>
+        <v>info@tpl.properties</v>
       </c>
       <c r="C802" t="str">
-        <v>07973 272334</v>
+        <v>07388570642</v>
       </c>
       <c r="D802" t="str">
         <v/>
@@ -32288,83 +32288,83 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>Tope</v>
+        <v xml:space="preserve">Tom Stayzo </v>
       </c>
       <c r="B803" t="str">
-        <v>info@aisiki.co.uk</v>
+        <v>direct@stayzo.co.uk</v>
       </c>
       <c r="C803" t="str">
-        <v>+44(0)7563372244</v>
+        <v>01494629629</v>
       </c>
       <c r="D803" t="str">
-        <v>AISIKI ACCOMMODATION</v>
+        <v>07740472525</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>Toreeq Alaran</v>
+        <v xml:space="preserve">Tony / Danny </v>
       </c>
       <c r="B804" t="str">
-        <v>toreeq.alaran@treasure-residentials.com</v>
+        <v>dfghj@rtyu.com</v>
       </c>
       <c r="C804" t="str">
-        <v>07704296298</v>
+        <v>07973 272334</v>
       </c>
       <c r="D804" t="str">
-        <v>Treasure Residentials</v>
+        <v/>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>Toyin Ogunwomoju</v>
+        <v>Tope</v>
       </c>
       <c r="B805" t="str">
-        <v>email@emaaaail.com</v>
+        <v>info@aisiki.co.uk</v>
       </c>
       <c r="C805" t="str">
-        <v>07835788872</v>
+        <v>+44(0)7563372244</v>
       </c>
       <c r="D805" t="str">
-        <v/>
+        <v>AISIKI ACCOMMODATION</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>Travel Nest</v>
+        <v>Toreeq Alaran</v>
       </c>
       <c r="B806" t="str">
-        <v>customers@travelnest.com</v>
+        <v>toreeq.alaran@treasure-residentials.com</v>
       </c>
       <c r="C806" t="str">
-        <v>+44 (0)333 666 6111</v>
+        <v>07704296298</v>
       </c>
       <c r="D806" t="str">
-        <v/>
+        <v>Treasure Residentials</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>Trinoi Hartwell</v>
+        <v>Toyin Ogunwomoju</v>
       </c>
       <c r="B807" t="str">
-        <v>Info@hartwellresidence.co.uk</v>
+        <v>email@emaaaail.com</v>
       </c>
       <c r="C807" t="str">
-        <v>07741 469 324</v>
+        <v>07835788872</v>
       </c>
       <c r="D807" t="str">
-        <v>Hartwell Residences</v>
+        <v/>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>TripleCHomes</v>
+        <v>Travel Nest</v>
       </c>
       <c r="B808" t="str">
-        <v>triplechomesuk@gmail.com</v>
+        <v>customers@travelnest.com</v>
       </c>
       <c r="C808" t="str">
-        <v>07868 781113</v>
+        <v>+44 (0)333 666 6111</v>
       </c>
       <c r="D808" t="str">
         <v/>
@@ -32372,27 +32372,27 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>Troy | Bethel Stays</v>
+        <v>Trinoi Hartwell</v>
       </c>
       <c r="B809" t="str">
-        <v>troy@bethelhomes.co.uk</v>
+        <v>Info@hartwellresidence.co.uk</v>
       </c>
       <c r="C809" t="str">
-        <v>07521426039</v>
+        <v>07741 469 324</v>
       </c>
       <c r="D809" t="str">
-        <v/>
+        <v>Hartwell Residences</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>Tudor | White Orchid Properties</v>
+        <v>TripleCHomes</v>
       </c>
       <c r="B810" t="str">
-        <v>info@woprelocation.com</v>
+        <v>triplechomesuk@gmail.com</v>
       </c>
       <c r="C810" t="str">
-        <v xml:space="preserve">+447704327362 </v>
+        <v>07868 781113</v>
       </c>
       <c r="D810" t="str">
         <v/>
@@ -32400,13 +32400,13 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>Ufirst Stays</v>
+        <v>Troy | Bethel Stays</v>
       </c>
       <c r="B811" t="str">
-        <v>hello@ufirststays.co.uk</v>
+        <v>troy@bethelhomes.co.uk</v>
       </c>
       <c r="C811" t="str">
-        <v>07480 304214</v>
+        <v>07521426039</v>
       </c>
       <c r="D811" t="str">
         <v/>
@@ -32414,13 +32414,13 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>Ultra Urban Apartments</v>
+        <v>Tudor | White Orchid Properties</v>
       </c>
       <c r="B812" t="str">
-        <v>darincapital@gmail.com</v>
+        <v>info@woprelocation.com</v>
       </c>
       <c r="C812" t="str">
-        <v xml:space="preserve">07875682962 </v>
+        <v xml:space="preserve">+447704327362 </v>
       </c>
       <c r="D812" t="str">
         <v/>
@@ -32428,27 +32428,27 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>Umair</v>
+        <v>Ufirst Stays</v>
       </c>
       <c r="B813" t="str">
-        <v>contact@archfieldresidences.com</v>
+        <v>hello@ufirststays.co.uk</v>
       </c>
       <c r="C813" t="str">
-        <v>020 8058 0028</v>
+        <v>07480 304214</v>
       </c>
       <c r="D813" t="str">
-        <v>archfieldresidences.com</v>
+        <v/>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>Umer Sheikh</v>
+        <v>Ultra Urban Apartments</v>
       </c>
       <c r="B814" t="str">
-        <v>Umer@fake.com</v>
+        <v>darincapital@gmail.com</v>
       </c>
       <c r="C814" t="str">
-        <v>07574 089805</v>
+        <v xml:space="preserve">07875682962 </v>
       </c>
       <c r="D814" t="str">
         <v/>
@@ -32456,153 +32456,153 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>Urban Stays</v>
+        <v>Umair</v>
       </c>
       <c r="B815" t="str">
-        <v>bookings@stayurbanrest.com</v>
+        <v>contact@archfieldresidences.com</v>
       </c>
       <c r="C815" t="str">
-        <v>+44 (0) 151 308 1776</v>
+        <v>020 8058 0028</v>
       </c>
       <c r="D815" t="str">
-        <v>Urban Stays</v>
+        <v>archfieldresidences.com</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>Valentine</v>
+        <v>Umer Sheikh</v>
       </c>
       <c r="B816" t="str">
-        <v>info@garlandinvestment.com</v>
+        <v>Umer@fake.com</v>
       </c>
       <c r="C816" t="str">
-        <v>07719742087</v>
+        <v>07574 089805</v>
       </c>
       <c r="D816" t="str">
-        <v>Garland Apartments</v>
+        <v/>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>Vanessa Zheng</v>
+        <v>Urban Stays</v>
       </c>
       <c r="B817" t="str">
-        <v>reservations@smartcorporatestays.com</v>
+        <v>bookings@stayurbanrest.com</v>
       </c>
       <c r="C817" t="str">
-        <v>+447454488112</v>
+        <v>+44 (0) 151 308 1776</v>
       </c>
       <c r="D817" t="str">
-        <v>Smart Corporate Stays</v>
+        <v>Urban Stays</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>Vaughan Property Group</v>
+        <v>Valentine</v>
       </c>
       <c r="B818" t="str">
-        <v>Info@vaughanpropertygroup.co.uk</v>
+        <v>info@garlandinvestment.com</v>
       </c>
       <c r="C818" t="str">
-        <v>0208 088 4191</v>
+        <v>07719742087</v>
       </c>
       <c r="D818" t="str">
-        <v>vaughanpropertygroup.co.uk</v>
+        <v>Garland Apartments</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>Veronica</v>
+        <v>Vanessa Zheng</v>
       </c>
       <c r="B819" t="str">
-        <v>info@airstayproperties.com</v>
+        <v>reservations@smartcorporatestays.com</v>
       </c>
       <c r="C819" t="str">
-        <v>07592294429</v>
+        <v>+447454488112</v>
       </c>
       <c r="D819" t="str">
-        <v>Air Stay Properties</v>
+        <v>Smart Corporate Stays</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>Vicky Poole</v>
+        <v>Vaughan Property Group</v>
       </c>
       <c r="B820" t="str">
-        <v>vicke@airnbbnot.com</v>
+        <v>Info@vaughanpropertygroup.co.uk</v>
       </c>
       <c r="C820" t="str">
-        <v>+447799888589</v>
+        <v>0208 088 4191</v>
       </c>
       <c r="D820" t="str">
-        <v/>
+        <v>vaughanpropertygroup.co.uk</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>Victoria Pollard</v>
+        <v>Veronica</v>
       </c>
       <c r="B821" t="str">
-        <v>info@lifes2short.org.uk</v>
+        <v>info@airstayproperties.com</v>
       </c>
       <c r="C821" t="str">
-        <v>07480 487948</v>
+        <v>07592294429</v>
       </c>
       <c r="D821" t="str">
-        <v>Lifes to Short</v>
+        <v>Air Stay Properties</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>Vipinbhai Patel</v>
+        <v>Vicky Poole</v>
       </c>
       <c r="B822" t="str">
-        <v>bookings@dwellersdelight.com</v>
+        <v>vicke@airnbbnot.com</v>
       </c>
       <c r="C822" t="str">
-        <v>07379 452644</v>
+        <v>+447799888589</v>
       </c>
       <c r="D822" t="str">
-        <v>Dwellers Delight Residentials</v>
+        <v/>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>Vista Stays</v>
+        <v>Victoria Pollard</v>
       </c>
       <c r="B823" t="str">
-        <v>bookings@vistastays.co.uk</v>
+        <v>info@lifes2short.org.uk</v>
       </c>
       <c r="C823" t="str">
-        <v>0333 090 7313</v>
+        <v>07480 487948</v>
       </c>
       <c r="D823" t="str">
-        <v/>
+        <v>Lifes to Short</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>Waleed Khalid</v>
+        <v>Vipinbhai Patel</v>
       </c>
       <c r="B824" t="str">
-        <v>dontknow@gmail.com</v>
+        <v>bookings@dwellersdelight.com</v>
       </c>
       <c r="C824" t="str">
-        <v>07930000039</v>
+        <v>07379 452644</v>
       </c>
       <c r="D824" t="str">
-        <v>La Casa Living Limited</v>
+        <v>Dwellers Delight Residentials</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>Waleed Khalid</v>
+        <v>Vista Stays</v>
       </c>
       <c r="B825" t="str">
-        <v>fakewaleed@gmail.com</v>
+        <v>bookings@vistastays.co.uk</v>
       </c>
       <c r="C825" t="str">
-        <v>+44 7930 000039</v>
+        <v>0333 090 7313</v>
       </c>
       <c r="D825" t="str">
         <v/>
@@ -32610,111 +32610,111 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>Walters Nsoh</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="B826" t="str">
-        <v>wjpartnerslimited@gmail.com</v>
+        <v>fakewaleed@gmail.com</v>
       </c>
       <c r="C826" t="str">
-        <v>07900018502</v>
+        <v>+44 7930 000039</v>
       </c>
       <c r="D826" t="str">
-        <v>W J Partners Limited</v>
+        <v/>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>We Are Renzo</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="B827" t="str">
-        <v>contact@renzoproperty.com</v>
+        <v>dontknow@gmail.com</v>
       </c>
       <c r="C827" t="str">
-        <v>01604 315710</v>
+        <v>07930000039</v>
       </c>
       <c r="D827" t="str">
-        <v>Renzo</v>
+        <v>La Casa Living Limited</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>Westbeachproperties</v>
+        <v>Walters Nsoh</v>
       </c>
       <c r="B828" t="str">
-        <v>kim@westbeachproperties.com</v>
+        <v>wjpartnerslimited@gmail.com</v>
       </c>
       <c r="C828" t="str">
-        <v>01273 911213</v>
+        <v>07900018502</v>
       </c>
       <c r="D828" t="str">
-        <v>West Beach Properties</v>
+        <v>W J Partners Limited</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>Will</v>
+        <v>We Are Renzo</v>
       </c>
       <c r="B829" t="str">
-        <v>info@2cholidays.co.uk</v>
+        <v>contact@renzoproperty.com</v>
       </c>
       <c r="C829" t="str">
-        <v>01362 470888</v>
+        <v>01604 315710</v>
       </c>
       <c r="D829" t="str">
-        <v>2cholidays.co.uk</v>
+        <v>Renzo</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>William John</v>
+        <v>Westbeachproperties</v>
       </c>
       <c r="B830" t="str">
-        <v>will@hastingsholidays.uk</v>
+        <v>kim@westbeachproperties.com</v>
       </c>
       <c r="C830" t="str">
-        <v>07743744881</v>
+        <v>01273 911213</v>
       </c>
       <c r="D830" t="str">
-        <v/>
+        <v>West Beach Properties</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>William Webb</v>
+        <v>Westciti</v>
       </c>
       <c r="B831" t="str">
-        <v>bankawebb@gmail.com</v>
+        <v>info@westciti.com</v>
       </c>
       <c r="C831" t="str">
-        <v>07766412006</v>
+        <v xml:space="preserve"> +44 (0) 333 5000 500</v>
       </c>
       <c r="D831" t="str">
-        <v>Webb &amp; Co Properties Ltd</v>
+        <v/>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>Xizhi</v>
+        <v>Will</v>
       </c>
       <c r="B832" t="str">
-        <v>dont@gmail.com</v>
+        <v>info@2cholidays.co.uk</v>
       </c>
       <c r="C832" t="str">
-        <v>+44 7477 458813</v>
+        <v>01362 470888</v>
       </c>
       <c r="D832" t="str">
-        <v/>
+        <v>2cholidays.co.uk</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v xml:space="preserve">Xizhi </v>
+        <v>William John</v>
       </c>
       <c r="B833" t="str">
-        <v>donot@email.com</v>
+        <v>will@hastingsholidays.uk</v>
       </c>
       <c r="C833" t="str">
-        <v xml:space="preserve"> +44 7477 458813</v>
+        <v>07743744881</v>
       </c>
       <c r="D833" t="str">
         <v/>
@@ -32722,125 +32722,125 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>Yanmei Chan</v>
+        <v>William Webb</v>
       </c>
       <c r="B834" t="str">
-        <v>bokmunc@gmail.com</v>
+        <v>bankawebb@gmail.com</v>
       </c>
       <c r="C834" t="str">
-        <v>07974 916396</v>
+        <v>07766412006</v>
       </c>
       <c r="D834" t="str">
-        <v/>
+        <v>Webb &amp; Co Properties Ltd</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>Yannick</v>
+        <v>Xizhi</v>
       </c>
       <c r="B835" t="str">
-        <v>enquires@snoozemovesstays.co.uk</v>
+        <v>dont@gmail.com</v>
       </c>
       <c r="C835" t="str">
-        <v>07535 799352</v>
+        <v>+44 7477 458813</v>
       </c>
       <c r="D835" t="str">
-        <v>Snooze Moves</v>
+        <v/>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>Yems</v>
+        <v xml:space="preserve">Xizhi </v>
       </c>
       <c r="B836" t="str">
-        <v>ert@dfg.com</v>
+        <v>donot@email.com</v>
       </c>
       <c r="C836" t="str">
-        <v>07956147630</v>
+        <v xml:space="preserve"> +44 7477 458813</v>
       </c>
       <c r="D836" t="str">
-        <v>Yems Enterprise LTD</v>
+        <v/>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>Yoko Property Management</v>
+        <v>Yanmei Chan</v>
       </c>
       <c r="B837" t="str">
-        <v>info@yokoproperty.co.uk</v>
+        <v>bokmunc@gmail.com</v>
       </c>
       <c r="C837" t="str">
-        <v>use whatsapp group / 0333 772 7478</v>
+        <v>07974 916396</v>
       </c>
       <c r="D837" t="str">
-        <v>Yoko Property Management</v>
+        <v/>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>YourLettings</v>
+        <v>Yannick</v>
       </c>
       <c r="B838" t="str">
-        <v>info@yourlettingsuk.com</v>
+        <v>enquires@snoozemovesstays.co.uk</v>
       </c>
       <c r="C838" t="str">
-        <v>01733711223</v>
+        <v>07535 799352</v>
       </c>
       <c r="D838" t="str">
-        <v xml:space="preserve">YourLettingsUK.com </v>
+        <v>Snooze Moves</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>Zainab</v>
+        <v>Yems</v>
       </c>
       <c r="B839" t="str">
-        <v>fake@Airbnb.com</v>
+        <v>ert@dfg.com</v>
       </c>
       <c r="C839" t="str">
-        <v>+44 7412 026604</v>
+        <v>07956147630</v>
       </c>
       <c r="D839" t="str">
-        <v/>
+        <v>Yems Enterprise LTD</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>Zaky</v>
+        <v>Yoko Property Management</v>
       </c>
       <c r="B840" t="str">
-        <v>gbcapitalproperties@outlook.com</v>
+        <v>info@yokoproperty.co.uk</v>
       </c>
       <c r="C840" t="str">
-        <v>+447379188217</v>
+        <v>use whatsapp group / 0333 772 7478</v>
       </c>
       <c r="D840" t="str">
-        <v>GB Capital Properties</v>
+        <v>Yoko Property Management</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>Zoe</v>
+        <v>YourLettings</v>
       </c>
       <c r="B841" t="str">
-        <v>book@staytysa.co.uk</v>
+        <v>info@yourlettingsuk.com</v>
       </c>
       <c r="C841" t="str">
-        <v>+442921690309</v>
+        <v>01733711223</v>
       </c>
       <c r="D841" t="str">
-        <v>Ty SA</v>
+        <v xml:space="preserve">YourLettingsUK.com </v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>accessible holiday escapes</v>
+        <v>Zainab</v>
       </c>
       <c r="B842" t="str">
-        <v>hello@accessibleholidayescapes.co.uk</v>
+        <v>fake@Airbnb.com</v>
       </c>
       <c r="C842" t="str">
-        <v>07881 802306</v>
+        <v>+44 7412 026604</v>
       </c>
       <c r="D842" t="str">
         <v/>
@@ -32848,41 +32848,41 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>https://jsmspropertymanagement.com/</v>
+        <v>Zaky</v>
       </c>
       <c r="B843" t="str">
-        <v>info@jsmspropertymanagement.com</v>
+        <v>gbcapitalproperties@outlook.com</v>
       </c>
       <c r="C843" t="str">
-        <v>000000000</v>
+        <v>+447379188217</v>
       </c>
       <c r="D843" t="str">
-        <v>jsmspropertymanagement.com</v>
+        <v>GB Capital Properties</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>https://www.stayatpeartree.com</v>
+        <v>Zoe</v>
       </c>
       <c r="B844" t="str">
-        <v>reception@stayatpeartree.com</v>
+        <v>book@staytysa.co.uk</v>
       </c>
       <c r="C844" t="str">
-        <v>01722 322 055</v>
+        <v>+442921690309</v>
       </c>
       <c r="D844" t="str">
-        <v/>
+        <v>Ty SA</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>luke stays</v>
+        <v>accessible holiday escapes</v>
       </c>
       <c r="B845" t="str">
-        <v>guest@lukestays.com</v>
+        <v>hello@accessibleholidayescapes.co.uk</v>
       </c>
       <c r="C845" t="str">
-        <v>01919338999</v>
+        <v>07881 802306</v>
       </c>
       <c r="D845" t="str">
         <v/>
@@ -32890,27 +32890,27 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>mosa</v>
+        <v>https://jsmspropertymanagement.com/</v>
       </c>
       <c r="B846" t="str">
-        <v>hello@mygetaways.co.uk</v>
+        <v>info@jsmspropertymanagement.com</v>
       </c>
       <c r="C846" t="str">
-        <v>+44 (0)1273 917900</v>
+        <v>000000000</v>
       </c>
       <c r="D846" t="str">
-        <v>mygetaways.co.uk</v>
+        <v>jsmspropertymanagement.com</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>moxyslough.com</v>
+        <v>https://www.stayatpeartree.com</v>
       </c>
       <c r="B847" t="str">
-        <v>Jakub.palyga@moxyslough.com</v>
+        <v>reception@stayatpeartree.com</v>
       </c>
       <c r="C847" t="str">
-        <v>44 (0)7502 531615</v>
+        <v>01722 322 055</v>
       </c>
       <c r="D847" t="str">
         <v/>
@@ -32918,13 +32918,13 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>oceanservicedapts.com</v>
+        <v>luke stays</v>
       </c>
       <c r="B848" t="str">
-        <v>stay@oceanservicedapts.com</v>
+        <v>guest@lukestays.com</v>
       </c>
       <c r="C848" t="str">
-        <v>0131 553 7394</v>
+        <v>01919338999</v>
       </c>
       <c r="D848" t="str">
         <v/>
@@ -32932,27 +32932,27 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>rachele Hayman</v>
+        <v>mosa</v>
       </c>
       <c r="B849" t="str">
-        <v>rachele@knightsbridgeapartments.co.uk</v>
+        <v>hello@mygetaways.co.uk</v>
       </c>
       <c r="C849" t="str">
-        <v>+447985521561</v>
+        <v>+44 (0)1273 917900</v>
       </c>
       <c r="D849" t="str">
-        <v/>
+        <v>mygetaways.co.uk</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>short stay homes</v>
+        <v>moxyslough.com</v>
       </c>
       <c r="B850" t="str">
-        <v>contact@shortstayhomes.co.uk</v>
+        <v>Jakub.palyga@moxyslough.com</v>
       </c>
       <c r="C850" t="str">
-        <v>01425 517 311</v>
+        <v>44 (0)7502 531615</v>
       </c>
       <c r="D850" t="str">
         <v/>
@@ -32960,13 +32960,13 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>worcesterluxuryapartments.co.uk</v>
+        <v>oceanservicedapts.com</v>
       </c>
       <c r="B851" t="str">
-        <v>info@worcesterluxuryapartments.co.uk</v>
+        <v>stay@oceanservicedapts.com</v>
       </c>
       <c r="C851" t="str">
-        <v>01905 706786</v>
+        <v>0131 553 7394</v>
       </c>
       <c r="D851" t="str">
         <v/>
@@ -32974,21 +32974,63 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
+        <v>rachele Hayman</v>
+      </c>
+      <c r="B852" t="str">
+        <v>rachele@knightsbridgeapartments.co.uk</v>
+      </c>
+      <c r="C852" t="str">
+        <v>+447985521561</v>
+      </c>
+      <c r="D852" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="str">
+        <v>short stay homes</v>
+      </c>
+      <c r="B853" t="str">
+        <v>contact@shortstayhomes.co.uk</v>
+      </c>
+      <c r="C853" t="str">
+        <v>01425 517 311</v>
+      </c>
+      <c r="D853" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v>worcesterluxuryapartments.co.uk</v>
+      </c>
+      <c r="B854" t="str">
+        <v>info@worcesterluxuryapartments.co.uk</v>
+      </c>
+      <c r="C854" t="str">
+        <v>01905 706786</v>
+      </c>
+      <c r="D854" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="str">
         <v>www.mazahomes.co.uk</v>
       </c>
-      <c r="B852" t="str">
+      <c r="B855" t="str">
         <v>info@mazahomes.co.uk</v>
       </c>
-      <c r="C852" t="str">
+      <c r="C855" t="str">
         <v>+44 7726 210060</v>
       </c>
-      <c r="D852" t="str">
+      <c r="D855" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D852"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D855"/>
   </ignoredErrors>
 </worksheet>
 </file>